--- a/hardware/v2.6/Planktoscope_V2.6_BOM.xlsx
+++ b/hardware/v2.6/Planktoscope_V2.6_BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Documents\GitHub\PlanktoScope\hardware\v2.6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045E360C-FE64-4F1D-ACCE-2E16E28FBF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F84E18-05ED-420F-8AC2-CBE940F16950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="225">
   <si>
     <t>PlanktoScope V2.6 BOM</t>
   </si>
@@ -152,9 +152,6 @@
     <t>Sold by FairScope with the Drivers with QC</t>
   </si>
   <si>
-    <t>Tube flexible Saint Gobain Tygon® (E-3603), Ø 3.2mm x Ø 6.4mm, L 15m Transparent</t>
-  </si>
-  <si>
     <t>ACF00007</t>
   </si>
   <si>
@@ -167,9 +164,6 @@
     <t>ProtoElectronics / PCBWay / ...</t>
   </si>
   <si>
-    <t>Tube flexible Saint Gobain Tygon® E-3603 PVC Special, Ø 1.6mm x Ø 3.2mm, L 15m Transparent</t>
-  </si>
-  <si>
     <t>ACF00002</t>
   </si>
   <si>
@@ -396,12 +390,6 @@
   </si>
   <si>
     <t>https://www.mouser.fr/ProductDetail/Adafruit/754?qs=GURawfaeGuBPXzWddhzfpQ%3D%3D</t>
-  </si>
-  <si>
-    <t>Connecting ribbon cable 30cm_2P_DoubleHead</t>
-  </si>
-  <si>
-    <t>https://fr.aliexpress.com/item/1005006085726477.html?spm=a2g0o.order_list.order_list_main.84.13cf5e5bjYNGGT&amp;gatewayAdapt=glo2fra</t>
   </si>
   <si>
     <t>Nylon Flat Insulating Washers M3 x 8mm x 1mm</t>
@@ -716,6 +704,15 @@
   </si>
   <si>
     <t>https://www.tectake.fr/valise-etanche-pour-appareil-photo-800574?tec_size=2343</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Flexibe Tube Saint Gobain Tygon® (E-3603), Ø 3.2mm x Ø 6.4mm, L 15m Transparent</t>
+  </si>
+  <si>
+    <t>Flexible Tube Saint Gobain Tygon® E-3603 PVC Special, Ø 1.6mm x Ø 3.2mm, L 15m Transparent</t>
   </si>
 </sst>
 </file>
@@ -1256,7 +1253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1279,13 +1276,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1308,13 +1303,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1334,6 +1326,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1552,7 +1548,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AV1028"/>
+  <dimension ref="A1:AV1027"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.7265625" customWidth="1"/>
@@ -1560,31 +1556,32 @@
     <col min="3" max="4" width="3.6328125" customWidth="1"/>
     <col min="5" max="5" width="32.08984375" customWidth="1"/>
     <col min="6" max="6" width="4.6328125" customWidth="1"/>
+    <col min="10" max="10" width="34.90625" customWidth="1"/>
     <col min="13" max="13" width="29.36328125" customWidth="1"/>
     <col min="15" max="15" width="9.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="12.5">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="48"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="43"/>
       <c r="L1" s="1"/>
-      <c r="M1" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="48"/>
+      <c r="M1" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="43"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
@@ -1625,11 +1622,11 @@
       <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="47"/>
-      <c r="E2" s="50"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="45"/>
       <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
@@ -1701,11 +1698,11 @@
       <c r="B3" s="8">
         <v>1</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="52"/>
-      <c r="E3" s="53"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
       <c r="F3" s="8">
         <v>1</v>
       </c>
@@ -1719,4808 +1716,4915 @@
       <c r="J3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="10"/>
-      <c r="M3" s="11" t="s">
+      <c r="K3" s="51" t="s">
+        <v>222</v>
+      </c>
+      <c r="M3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="N3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="O3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="P3" s="12" t="s">
         <v>18</v>
       </c>
+      <c r="Q3" s="50" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="4" spans="1:48" ht="12.5">
-      <c r="A4" s="14">
+      <c r="A4" s="13">
         <v>2</v>
       </c>
-      <c r="B4" s="15">
-        <v>1</v>
-      </c>
-      <c r="C4" s="40" t="s">
+      <c r="B4" s="14">
+        <v>1</v>
+      </c>
+      <c r="C4" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="42"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="15">
-        <v>1</v>
-      </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15" t="s">
+      <c r="D4" s="37"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="14">
+        <v>1</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="17" t="s">
+      <c r="J4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="18"/>
-      <c r="M4" s="14" t="s">
+      <c r="K4" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="M4" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="N4" s="19" t="s">
+      <c r="N4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="19" t="s">
+      <c r="O4" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="P4" s="20" t="s">
+      <c r="P4" s="18" t="s">
         <v>24</v>
       </c>
+      <c r="Q4" s="50" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="5" spans="1:48" ht="12.5">
-      <c r="A5" s="14">
+      <c r="A5" s="13">
         <v>3</v>
       </c>
-      <c r="B5" s="15">
-        <v>1</v>
-      </c>
-      <c r="C5" s="40" t="s">
+      <c r="B5" s="14">
+        <v>1</v>
+      </c>
+      <c r="C5" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="42"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="15">
+      <c r="D5" s="37"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="14">
         <v>2</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="21" t="s">
+      <c r="G5" s="14"/>
+      <c r="H5" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="18"/>
-      <c r="M5" s="14" t="s">
+      <c r="K5" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="M5" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="N5" s="19" t="s">
+      <c r="N5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="19" t="s">
+      <c r="O5" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="P5" s="20" t="s">
+      <c r="P5" s="18" t="s">
         <v>31</v>
       </c>
+      <c r="Q5" s="50" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="6" spans="1:48" ht="12.5">
-      <c r="A6" s="14">
+      <c r="A6" s="7">
         <v>4</v>
       </c>
-      <c r="B6" s="15">
-        <v>1</v>
-      </c>
-      <c r="C6" s="40" t="s">
+      <c r="B6" s="14">
+        <v>1</v>
+      </c>
+      <c r="C6" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="15">
-        <v>1</v>
-      </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15" t="s">
+      <c r="D6" s="37"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="14">
+        <v>1</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="22" t="s">
+      <c r="J6" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="K6" s="18"/>
-      <c r="M6" s="14" t="s">
+      <c r="K6" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="M6" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="19" t="s">
+      <c r="N6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O6" s="19" t="s">
+      <c r="O6" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="P6" s="20" t="s">
+      <c r="P6" s="18" t="s">
         <v>38</v>
       </c>
+      <c r="Q6" s="50" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="7" spans="1:48" ht="12.5">
-      <c r="A7" s="14">
+      <c r="A7" s="13">
         <v>5</v>
       </c>
-      <c r="B7" s="15">
-        <v>1</v>
-      </c>
-      <c r="C7" s="40" t="s">
+      <c r="B7" s="14">
+        <v>1</v>
+      </c>
+      <c r="C7" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="42"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="15">
-        <v>1</v>
-      </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15" t="s">
+      <c r="D7" s="37"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="14">
+        <v>1</v>
+      </c>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="18"/>
-      <c r="M7" s="23" t="s">
+      <c r="K7" s="16"/>
+      <c r="M7" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="O7" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="19" t="s">
+      <c r="P7" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q7" s="50" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:48" ht="12.5">
+      <c r="A8" s="13">
+        <v>6</v>
+      </c>
+      <c r="B8" s="14">
+        <v>2</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="36"/>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="16"/>
+      <c r="M8" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="N8" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="19" t="s">
+      <c r="O8" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="P8" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q8" s="50" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:48" ht="12.5">
+      <c r="A9" s="7">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14">
+        <v>2</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="36"/>
+      <c r="F9" s="14">
+        <v>1</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:48" ht="12.5">
+      <c r="A10" s="13">
+        <v>8</v>
+      </c>
+      <c r="B10" s="14">
+        <v>2</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="36"/>
+      <c r="F10" s="14">
+        <v>4</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="K10" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:48" ht="12.5">
+      <c r="A11" s="13">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14">
+        <v>2</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="36"/>
+      <c r="F11" s="14">
+        <v>4</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:48" ht="12.5">
+      <c r="A12" s="7">
+        <v>10</v>
+      </c>
+      <c r="B12" s="14">
+        <v>2</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="36"/>
+      <c r="F12" s="14">
+        <v>2</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="16"/>
+      <c r="M12" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="43"/>
+    </row>
+    <row r="13" spans="1:48" ht="15" customHeight="1">
+      <c r="A13" s="13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="14">
+        <v>3</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="14">
+        <v>2</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K13" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="M13" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="N13" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="O13" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:48" ht="12.5">
+      <c r="A14" s="13">
+        <v>12</v>
+      </c>
+      <c r="B14" s="14">
+        <v>3</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="14">
+        <v>2</v>
+      </c>
+      <c r="G14" s="14"/>
+      <c r="H14" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K14" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="N14" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="O14" s="11">
+        <v>1441020</v>
+      </c>
+      <c r="P14" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q14" s="50" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="15" spans="1:48" ht="12.5">
+      <c r="A15" s="7">
+        <v>13</v>
+      </c>
+      <c r="B15" s="14">
+        <v>1</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="37"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="K15" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="O15" s="17">
+        <v>1441021</v>
+      </c>
+      <c r="P15" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q15" s="50" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="16" spans="1:48" ht="12.5">
+      <c r="A16" s="13">
+        <v>14</v>
+      </c>
+      <c r="B16" s="14">
+        <v>1</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="37"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="14">
+        <v>1</v>
+      </c>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" s="16"/>
+      <c r="M16" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="P16" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q16" s="50" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="12.5">
+      <c r="A17" s="13">
+        <v>15</v>
+      </c>
+      <c r="B17" s="14">
+        <v>2</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="36"/>
+      <c r="F17" s="14">
+        <v>1</v>
+      </c>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="K17" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="M17" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="O17" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="P17" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q17" s="50" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="12.5">
+      <c r="A18" s="7">
+        <v>16</v>
+      </c>
+      <c r="B18" s="14">
+        <v>2</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="36"/>
+      <c r="F18" s="14">
+        <v>1</v>
+      </c>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="K18" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="M18" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="O18" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="P18" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q18" s="50" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="12.5">
+      <c r="A19" s="13">
+        <v>17</v>
+      </c>
+      <c r="B19" s="14">
+        <v>2</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="36"/>
+      <c r="F19" s="14">
+        <v>1</v>
+      </c>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K19" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="M19" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="N19" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="O19" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="P19" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q19" s="50" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="12.5">
+      <c r="A20" s="13">
+        <v>18</v>
+      </c>
+      <c r="B20" s="14">
+        <v>2</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="36"/>
+      <c r="F20" s="14">
+        <v>1</v>
+      </c>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="K20" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="12.5">
+      <c r="A21" s="7">
+        <v>19</v>
+      </c>
+      <c r="B21" s="14">
+        <v>2</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" s="36"/>
+      <c r="F21" s="14">
+        <v>2</v>
+      </c>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="K21" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="12.5">
+      <c r="A22" s="13">
+        <v>20</v>
+      </c>
+      <c r="B22" s="14">
+        <v>1</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" s="37"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="14">
+        <v>1</v>
+      </c>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22" s="16"/>
+    </row>
+    <row r="23" spans="1:17" ht="12.5">
+      <c r="A23" s="13">
+        <v>21</v>
+      </c>
+      <c r="B23" s="14">
+        <v>2</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" s="36"/>
+      <c r="F23" s="14">
+        <v>1</v>
+      </c>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="K23" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="12.5">
+      <c r="A24" s="7">
+        <v>22</v>
+      </c>
+      <c r="B24" s="14">
+        <v>2</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" s="36"/>
+      <c r="F24" s="14">
+        <v>1</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="K24" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="12.5">
+      <c r="A25" s="13">
+        <v>23</v>
+      </c>
+      <c r="B25" s="14">
+        <v>1</v>
+      </c>
+      <c r="C25" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="37"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="14">
+        <v>2</v>
+      </c>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="I25" s="14"/>
+      <c r="J25" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="K25" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="12.5">
+      <c r="A26" s="13">
+        <v>24</v>
+      </c>
+      <c r="B26" s="14">
+        <v>1</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="37"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="14">
+        <v>1</v>
+      </c>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="16"/>
+    </row>
+    <row r="27" spans="1:17" ht="12.5">
+      <c r="A27" s="7">
+        <v>25</v>
+      </c>
+      <c r="B27" s="14">
+        <v>2</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" s="36"/>
+      <c r="F27" s="14">
+        <v>1</v>
+      </c>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="K27" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="12.5">
+      <c r="A28" s="13">
+        <v>26</v>
+      </c>
+      <c r="B28" s="14">
+        <v>2</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="36"/>
+      <c r="F28" s="14">
+        <v>1</v>
+      </c>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="12.5">
+      <c r="A29" s="13">
+        <v>27</v>
+      </c>
+      <c r="B29" s="14">
+        <v>1</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" s="37"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="14">
+        <v>1</v>
+      </c>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="16"/>
+    </row>
+    <row r="30" spans="1:17" ht="12.5">
+      <c r="A30" s="7">
+        <v>28</v>
+      </c>
+      <c r="B30" s="14">
+        <v>2</v>
+      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" s="36"/>
+      <c r="F30" s="14">
+        <v>1</v>
+      </c>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="K30" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="12.5">
+      <c r="A31" s="13">
+        <v>29</v>
+      </c>
+      <c r="B31" s="14">
+        <v>2</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="D31" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31" s="36"/>
+      <c r="F31" s="14">
+        <v>1</v>
+      </c>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="12.5">
+      <c r="A32" s="13">
+        <v>30</v>
+      </c>
+      <c r="B32" s="14">
+        <v>1</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" s="37"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="14">
+        <v>1</v>
+      </c>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="K32" s="16"/>
+    </row>
+    <row r="33" spans="1:11" ht="12.5">
+      <c r="A33" s="7">
+        <v>31</v>
+      </c>
+      <c r="B33" s="14">
+        <v>2</v>
+      </c>
+      <c r="C33" s="14"/>
+      <c r="D33" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="E33" s="36"/>
+      <c r="F33" s="14">
+        <v>1</v>
+      </c>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="K33" s="16"/>
+    </row>
+    <row r="34" spans="1:11" ht="12.5">
+      <c r="A34" s="13">
+        <v>32</v>
+      </c>
+      <c r="B34" s="14">
+        <v>2</v>
+      </c>
+      <c r="C34" s="14"/>
+      <c r="D34" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="E34" s="36"/>
+      <c r="F34" s="14">
+        <v>10</v>
+      </c>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="J34" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="K34" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="12.5">
+      <c r="A35" s="13">
+        <v>33</v>
+      </c>
+      <c r="B35" s="14">
+        <v>2</v>
+      </c>
+      <c r="C35" s="14"/>
+      <c r="D35" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="E35" s="36"/>
+      <c r="F35" s="14">
+        <v>4</v>
+      </c>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="J35" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="K35" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="12.5">
+      <c r="A36" s="7">
+        <v>34</v>
+      </c>
+      <c r="B36" s="14">
+        <v>2</v>
+      </c>
+      <c r="C36" s="14"/>
+      <c r="D36" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="E36" s="36"/>
+      <c r="F36" s="14">
+        <v>16</v>
+      </c>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="K36" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="12.5">
+      <c r="A37" s="13">
+        <v>35</v>
+      </c>
+      <c r="B37" s="14">
+        <v>1</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="D37" s="37"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="14">
+        <v>2</v>
+      </c>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="I37" s="14"/>
+      <c r="J37" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="K37" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="12.5">
+      <c r="A38" s="13">
+        <v>36</v>
+      </c>
+      <c r="B38" s="14">
+        <v>1</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="D38" s="37"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="14">
+        <v>1</v>
+      </c>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="K38" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="12.5">
+      <c r="A39" s="7">
+        <v>37</v>
+      </c>
+      <c r="B39" s="14">
+        <v>1</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D39" s="37"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="14">
+        <v>2</v>
+      </c>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="K39" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="12.5">
+      <c r="A40" s="13">
+        <v>38</v>
+      </c>
+      <c r="B40" s="14">
+        <v>1</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" s="37"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="14">
+        <v>32</v>
+      </c>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="K40" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="12.5">
+      <c r="A41" s="13">
+        <v>39</v>
+      </c>
+      <c r="B41" s="14">
+        <v>1</v>
+      </c>
+      <c r="C41" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" s="37"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="14">
+        <v>32</v>
+      </c>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="K41" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="12.5">
+      <c r="A42" s="7">
+        <v>40</v>
+      </c>
+      <c r="B42" s="14">
+        <v>1</v>
+      </c>
+      <c r="C42" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="D42" s="37"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="14">
+        <v>6</v>
+      </c>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="J42" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="K42" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="12.5">
+      <c r="A43" s="13">
+        <v>41</v>
+      </c>
+      <c r="B43" s="14">
+        <v>1</v>
+      </c>
+      <c r="C43" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="D43" s="37"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="14">
+        <v>4</v>
+      </c>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="J43" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="K43" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="12.5">
+      <c r="A44" s="13">
+        <v>42</v>
+      </c>
+      <c r="B44" s="14">
+        <v>1</v>
+      </c>
+      <c r="C44" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="D44" s="37"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="14">
+        <v>4</v>
+      </c>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="K44" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="12.5">
+      <c r="A45" s="7">
+        <v>43</v>
+      </c>
+      <c r="B45" s="14">
+        <v>1</v>
+      </c>
+      <c r="C45" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" s="37"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="14">
+        <v>4</v>
+      </c>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="J45" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="K45" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="12.5">
+      <c r="A46" s="13">
         <v>44</v>
       </c>
-      <c r="P7" s="20" t="s">
+      <c r="B46" s="14">
+        <v>1</v>
+      </c>
+      <c r="C46" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="D46" s="37"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="14">
+        <v>4</v>
+      </c>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="J46" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="K46" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="12.5">
+      <c r="A47" s="13">
         <v>45</v>
       </c>
-    </row>
-    <row r="8" spans="1:48" ht="12.5">
-      <c r="A8" s="14">
-        <v>6</v>
-      </c>
-      <c r="B8" s="15">
+      <c r="B47" s="14">
+        <v>1</v>
+      </c>
+      <c r="C47" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="D47" s="37"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="14">
+        <v>4</v>
+      </c>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="J47" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="K47" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="12.5">
+      <c r="A48" s="7">
+        <v>46</v>
+      </c>
+      <c r="B48" s="14">
+        <v>1</v>
+      </c>
+      <c r="C48" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="D48" s="37"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="14">
+        <v>4</v>
+      </c>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="J48" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="K48" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="12.5">
+      <c r="A49" s="13">
+        <v>47</v>
+      </c>
+      <c r="B49" s="14">
+        <v>1</v>
+      </c>
+      <c r="C49" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="D49" s="37"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="14">
+        <v>1</v>
+      </c>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="I49" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="J49" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="K49" s="16"/>
+    </row>
+    <row r="50" spans="1:11" ht="12.5">
+      <c r="A50" s="13">
+        <v>48</v>
+      </c>
+      <c r="B50" s="14">
         <v>2</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="41"/>
-      <c r="F8" s="15">
-        <v>1</v>
-      </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="18"/>
-      <c r="M8" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="N8" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="O8" s="25" t="s">
+      <c r="C50" s="14"/>
+      <c r="D50" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="E50" s="36"/>
+      <c r="F50" s="14">
+        <v>3</v>
+      </c>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="J50" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="K50" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="12.5">
+      <c r="A51" s="7">
         <v>49</v>
       </c>
-      <c r="P8" s="26" t="s">
+      <c r="B51" s="14">
+        <v>2</v>
+      </c>
+      <c r="C51" s="14"/>
+      <c r="D51" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="E51" s="36"/>
+      <c r="F51" s="14">
+        <v>2</v>
+      </c>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="I51" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="J51" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="K51" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="12.5">
+      <c r="A52" s="13">
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:48" ht="12.5">
-      <c r="A9" s="14">
-        <v>7</v>
-      </c>
-      <c r="B9" s="15">
+      <c r="B52" s="14">
         <v>2</v>
       </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="40" t="s">
+      <c r="C52" s="14"/>
+      <c r="D52" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="E52" s="36"/>
+      <c r="F52" s="14">
+        <v>1</v>
+      </c>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I52" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="J52" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="K52" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="12.5">
+      <c r="A53" s="13">
         <v>51</v>
       </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="15">
-        <v>1</v>
-      </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="15" t="s">
+      <c r="B53" s="14">
+        <v>1</v>
+      </c>
+      <c r="C53" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="D53" s="37"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="14">
+        <v>1</v>
+      </c>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="16"/>
+    </row>
+    <row r="54" spans="1:11" ht="12.5">
+      <c r="A54" s="7">
         <v>52</v>
       </c>
-      <c r="J9" s="22" t="s">
+      <c r="B54" s="14">
+        <v>2</v>
+      </c>
+      <c r="C54" s="14"/>
+      <c r="D54" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="E54" s="36"/>
+      <c r="F54" s="14">
+        <v>1</v>
+      </c>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="I54" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J54" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="K54" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="12.5">
+      <c r="A55" s="13">
         <v>53</v>
       </c>
-      <c r="K9" s="18"/>
-    </row>
-    <row r="10" spans="1:48" ht="12.5">
-      <c r="A10" s="14">
-        <v>8</v>
-      </c>
-      <c r="B10" s="15">
+      <c r="B55" s="14">
         <v>2</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="40" t="s">
+      <c r="C55" s="14"/>
+      <c r="D55" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="E55" s="36"/>
+      <c r="F55" s="14">
+        <v>1</v>
+      </c>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="J55" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="K55" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="12.5">
+      <c r="A56" s="13">
         <v>54</v>
       </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="15">
-        <v>4</v>
-      </c>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15" t="s">
+      <c r="B56" s="14">
+        <v>2</v>
+      </c>
+      <c r="C56" s="14"/>
+      <c r="D56" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="E56" s="36"/>
+      <c r="F56" s="14">
+        <v>1</v>
+      </c>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I56" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="J56" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="K56" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="12.5">
+      <c r="A57" s="7">
         <v>55</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="B57" s="14">
+        <v>1</v>
+      </c>
+      <c r="C57" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="D57" s="37"/>
+      <c r="E57" s="36"/>
+      <c r="F57" s="14">
+        <v>1</v>
+      </c>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="J57" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="K57" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="12.5">
+      <c r="A58" s="13">
         <v>56</v>
       </c>
-      <c r="J10" s="22" t="s">
+      <c r="B58" s="14">
+        <v>1</v>
+      </c>
+      <c r="C58" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="D58" s="37"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="14">
+        <v>1</v>
+      </c>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="I58" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="J58" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="K58" s="16"/>
+    </row>
+    <row r="59" spans="1:11" ht="12.5">
+      <c r="A59" s="13">
         <v>57</v>
       </c>
-      <c r="K10" s="18"/>
-    </row>
-    <row r="11" spans="1:48" ht="12.5">
-      <c r="A11" s="14">
-        <v>9</v>
-      </c>
-      <c r="B11" s="15">
+      <c r="B59" s="14">
         <v>2</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="40" t="s">
+      <c r="C59" s="14"/>
+      <c r="D59" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="E59" s="36"/>
+      <c r="F59" s="14">
+        <v>1</v>
+      </c>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I59" s="14"/>
+      <c r="J59" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="K59" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="12.5">
+      <c r="A60" s="7">
         <v>58</v>
       </c>
-      <c r="E11" s="41"/>
-      <c r="F11" s="15">
-        <v>4</v>
-      </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="I11" s="15" t="s">
+      <c r="B60" s="14">
+        <v>2</v>
+      </c>
+      <c r="C60" s="14"/>
+      <c r="D60" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="E60" s="36"/>
+      <c r="F60" s="14">
+        <v>1</v>
+      </c>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="I60" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="J60" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="K60" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="12.5">
+      <c r="A61" s="13">
         <v>59</v>
       </c>
-      <c r="J11" s="22" t="s">
+      <c r="B61" s="14">
+        <v>2</v>
+      </c>
+      <c r="C61" s="14"/>
+      <c r="D61" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="E61" s="36"/>
+      <c r="F61" s="14">
+        <v>1</v>
+      </c>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="K11" s="18"/>
-    </row>
-    <row r="12" spans="1:48" ht="12.5">
-      <c r="A12" s="14">
-        <v>10</v>
-      </c>
-      <c r="B12" s="15">
-        <v>2</v>
-      </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="40" t="s">
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="16"/>
+    </row>
+    <row r="62" spans="1:11" ht="12.5">
+      <c r="A62" s="13">
+        <v>60</v>
+      </c>
+      <c r="B62" s="14">
+        <v>3</v>
+      </c>
+      <c r="C62" s="14"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F62" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="I62" s="14"/>
+      <c r="J62" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="12.5">
+      <c r="A63" s="7">
         <v>61</v>
       </c>
-      <c r="E12" s="41"/>
-      <c r="F12" s="15">
-        <v>2</v>
-      </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15" t="s">
+      <c r="B63" s="14">
+        <v>3</v>
+      </c>
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="F63" s="14">
+        <v>1</v>
+      </c>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="I63" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="J63" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="K63" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="12.5">
+      <c r="A64" s="13">
         <v>62</v>
       </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="18"/>
-      <c r="M12" s="46" t="s">
+      <c r="B64" s="14">
+        <v>1</v>
+      </c>
+      <c r="C64" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="D64" s="37"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="14">
+        <v>1</v>
+      </c>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="I64" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="J64" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="K64" s="16"/>
+    </row>
+    <row r="65" spans="1:11" ht="12.5">
+      <c r="A65" s="13">
         <v>63</v>
       </c>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="48"/>
-    </row>
-    <row r="13" spans="1:48" ht="15" customHeight="1">
-      <c r="A13" s="14">
-        <v>11</v>
-      </c>
-      <c r="B13" s="15">
-        <v>3</v>
-      </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15" t="s">
+      <c r="B65" s="14">
+        <v>1</v>
+      </c>
+      <c r="C65" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="D65" s="37"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="14">
+        <v>1</v>
+      </c>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="I65" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="J65" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="K65" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="12.5">
+      <c r="A66" s="7">
         <v>64</v>
       </c>
-      <c r="F13" s="15">
-        <v>2</v>
-      </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15" t="s">
+      <c r="B66" s="14">
+        <v>1</v>
+      </c>
+      <c r="C66" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="D66" s="37"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="14">
+        <v>1</v>
+      </c>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="I66" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="J66" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="K66" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="12.5">
+      <c r="A67" s="13">
         <v>65</v>
       </c>
-      <c r="I13" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="K13" s="18"/>
-      <c r="M13" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="N13" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="O13" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="P13" s="29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:48" ht="12.5">
-      <c r="A14" s="14">
-        <v>12</v>
-      </c>
-      <c r="B14" s="15">
-        <v>3</v>
-      </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="15">
-        <v>2</v>
-      </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="J14" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="K14" s="18"/>
-      <c r="M14" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="N14" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="O14" s="12">
-        <v>1441020</v>
-      </c>
-      <c r="P14" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:48" ht="12.5">
-      <c r="A15" s="14">
-        <v>13</v>
-      </c>
-      <c r="B15" s="15">
-        <v>1</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="J15" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="K15" s="18"/>
-      <c r="M15" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="N15" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="O15" s="19">
-        <v>1441021</v>
-      </c>
-      <c r="P15" s="20" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:48" ht="12.5">
-      <c r="A16" s="14">
-        <v>14</v>
-      </c>
-      <c r="B16" s="15">
-        <v>1</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="15">
-        <v>1</v>
-      </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="J16" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="K16" s="18"/>
-      <c r="M16" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="N16" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="O16" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="P16" s="20" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="12.5">
-      <c r="A17" s="14">
-        <v>15</v>
-      </c>
-      <c r="B17" s="15">
-        <v>2</v>
-      </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" s="41"/>
-      <c r="F17" s="15">
-        <v>1</v>
-      </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="J17" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="K17" s="18"/>
-      <c r="M17" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="N17" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="O17" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="P17" s="20" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="12.5">
-      <c r="A18" s="14">
-        <v>16</v>
-      </c>
-      <c r="B18" s="15">
-        <v>2</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" s="41"/>
-      <c r="F18" s="15">
-        <v>1</v>
-      </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="J18" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="K18" s="18"/>
-      <c r="M18" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="N18" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="O18" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="P18" s="31" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="12.5">
-      <c r="A19" s="14">
-        <v>17</v>
-      </c>
-      <c r="B19" s="15">
-        <v>2</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" s="41"/>
-      <c r="F19" s="15">
-        <v>1</v>
-      </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="I19" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="J19" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="K19" s="18"/>
-      <c r="M19" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="N19" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="O19" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="P19" s="26" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="12.5">
-      <c r="A20" s="14">
-        <v>18</v>
-      </c>
-      <c r="B20" s="15">
-        <v>2</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="E20" s="41"/>
-      <c r="F20" s="15">
-        <v>1</v>
-      </c>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="J20" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="K20" s="18"/>
-    </row>
-    <row r="21" spans="1:16" ht="12.5">
-      <c r="A21" s="14">
-        <v>19</v>
-      </c>
-      <c r="B21" s="15">
-        <v>2</v>
-      </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="E21" s="41"/>
-      <c r="F21" s="15">
-        <v>2</v>
-      </c>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="J21" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="K21" s="18"/>
-    </row>
-    <row r="22" spans="1:16" ht="12.5">
-      <c r="A22" s="14">
-        <v>20</v>
-      </c>
-      <c r="B22" s="15">
-        <v>1</v>
-      </c>
-      <c r="C22" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="15">
-        <v>1</v>
-      </c>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="J22" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="K22" s="18"/>
-    </row>
-    <row r="23" spans="1:16" ht="12.5">
-      <c r="A23" s="14">
-        <v>21</v>
-      </c>
-      <c r="B23" s="15">
-        <v>2</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="E23" s="41"/>
-      <c r="F23" s="15">
-        <v>1</v>
-      </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="J23" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="K23" s="18"/>
-    </row>
-    <row r="24" spans="1:16" ht="12.5">
-      <c r="A24" s="14">
-        <v>22</v>
-      </c>
-      <c r="B24" s="15">
-        <v>2</v>
-      </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="E24" s="41"/>
-      <c r="F24" s="15">
-        <v>1</v>
-      </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J24" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="K24" s="18"/>
-    </row>
-    <row r="25" spans="1:16" ht="12.5">
-      <c r="A25" s="14">
-        <v>23</v>
-      </c>
-      <c r="B25" s="15">
-        <v>1</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D25" s="33"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="15">
-        <v>1</v>
-      </c>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="I25" s="15"/>
-      <c r="J25" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="K25" s="18"/>
-    </row>
-    <row r="26" spans="1:16" ht="12.5">
-      <c r="A26" s="14">
-        <v>24</v>
-      </c>
-      <c r="B26" s="15">
-        <v>1</v>
-      </c>
-      <c r="C26" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="D26" s="42"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="15">
-        <v>2</v>
-      </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="I26" s="15"/>
-      <c r="J26" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="K26" s="18"/>
-    </row>
-    <row r="27" spans="1:16" ht="12.5">
-      <c r="A27" s="14">
-        <v>25</v>
-      </c>
-      <c r="B27" s="15">
-        <v>1</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="D27" s="42"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="15">
-        <v>1</v>
-      </c>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="18"/>
-    </row>
-    <row r="28" spans="1:16" ht="12.5">
-      <c r="A28" s="14">
-        <v>26</v>
-      </c>
-      <c r="B28" s="15">
-        <v>2</v>
-      </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="E28" s="41"/>
-      <c r="F28" s="15">
-        <v>1</v>
-      </c>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="J28" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="K28" s="18"/>
-    </row>
-    <row r="29" spans="1:16" ht="12.5">
-      <c r="A29" s="14">
-        <v>27</v>
-      </c>
-      <c r="B29" s="15">
-        <v>2</v>
-      </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="54" t="s">
-        <v>134</v>
-      </c>
-      <c r="E29" s="41"/>
-      <c r="F29" s="15">
-        <v>1</v>
-      </c>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="I29" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="J29" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="K29" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="12.5">
-      <c r="A30" s="14">
-        <v>28</v>
-      </c>
-      <c r="B30" s="15">
-        <v>1</v>
-      </c>
-      <c r="C30" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="D30" s="42"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="15">
-        <v>1</v>
-      </c>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="18"/>
-    </row>
-    <row r="31" spans="1:16" ht="12.5">
-      <c r="A31" s="14">
-        <v>29</v>
-      </c>
-      <c r="B31" s="15">
-        <v>2</v>
-      </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="E31" s="41"/>
-      <c r="F31" s="15">
-        <v>1</v>
-      </c>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="I31" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="J31" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="K31" s="18"/>
-    </row>
-    <row r="32" spans="1:16" ht="12.5">
-      <c r="A32" s="14">
-        <v>30</v>
-      </c>
-      <c r="B32" s="15">
-        <v>2</v>
-      </c>
-      <c r="C32" s="21"/>
-      <c r="D32" s="54" t="s">
-        <v>134</v>
-      </c>
-      <c r="E32" s="41"/>
-      <c r="F32" s="15">
-        <v>1</v>
-      </c>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="I32" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="J32" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="K32" s="18" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="12.5">
-      <c r="A33" s="14">
-        <v>31</v>
-      </c>
-      <c r="B33" s="15">
-        <v>1</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="D33" s="42"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="15">
-        <v>1</v>
-      </c>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I33" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="J33" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="K33" s="18"/>
-    </row>
-    <row r="34" spans="1:11" ht="12.5">
-      <c r="A34" s="14">
-        <v>32</v>
-      </c>
-      <c r="B34" s="15">
-        <v>2</v>
-      </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="E34" s="41"/>
-      <c r="F34" s="15">
-        <v>1</v>
-      </c>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I34" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="J34" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="K34" s="18"/>
-    </row>
-    <row r="35" spans="1:11" ht="12.5">
-      <c r="A35" s="14">
-        <v>33</v>
-      </c>
-      <c r="B35" s="15">
-        <v>2</v>
-      </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="40" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35" s="41"/>
-      <c r="F35" s="15">
-        <v>6</v>
-      </c>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="I35" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="J35" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="K35" s="18"/>
-    </row>
-    <row r="36" spans="1:11" ht="12.5">
-      <c r="A36" s="14">
-        <v>34</v>
-      </c>
-      <c r="B36" s="15">
-        <v>2</v>
-      </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="E36" s="41"/>
-      <c r="F36" s="15">
-        <v>4</v>
-      </c>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="I36" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="J36" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="K36" s="18"/>
-    </row>
-    <row r="37" spans="1:11" ht="12.5">
-      <c r="A37" s="14">
-        <v>35</v>
-      </c>
-      <c r="B37" s="15">
-        <v>2</v>
-      </c>
-      <c r="C37" s="15"/>
-      <c r="D37" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="E37" s="41"/>
-      <c r="F37" s="15">
-        <v>16</v>
-      </c>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="I37" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="J37" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="K37" s="18"/>
-    </row>
-    <row r="38" spans="1:11" ht="12.5">
-      <c r="A38" s="14">
-        <v>36</v>
-      </c>
-      <c r="B38" s="15">
-        <v>1</v>
-      </c>
-      <c r="C38" s="40" t="s">
-        <v>156</v>
-      </c>
-      <c r="D38" s="42"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="15">
-        <v>2</v>
-      </c>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="I38" s="15"/>
-      <c r="J38" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="K38" s="18"/>
-    </row>
-    <row r="39" spans="1:11" ht="12.5">
-      <c r="A39" s="14">
-        <v>37</v>
-      </c>
-      <c r="B39" s="15">
-        <v>1</v>
-      </c>
-      <c r="C39" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="D39" s="42"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="15">
-        <v>1</v>
-      </c>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="J39" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="K39" s="18"/>
-    </row>
-    <row r="40" spans="1:11" ht="12.5">
-      <c r="A40" s="14">
-        <v>38</v>
-      </c>
-      <c r="B40" s="15">
-        <v>1</v>
-      </c>
-      <c r="C40" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="D40" s="42"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="15">
-        <v>2</v>
-      </c>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="I40" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="J40" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="K40" s="18"/>
-    </row>
-    <row r="41" spans="1:11" ht="12.5">
-      <c r="A41" s="14">
-        <v>39</v>
-      </c>
-      <c r="B41" s="15">
-        <v>1</v>
-      </c>
-      <c r="C41" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="D41" s="42"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="15">
-        <v>32</v>
-      </c>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="I41" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="J41" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="K41" s="18"/>
-    </row>
-    <row r="42" spans="1:11" ht="12.5">
-      <c r="A42" s="14">
-        <v>40</v>
-      </c>
-      <c r="B42" s="15">
-        <v>1</v>
-      </c>
-      <c r="C42" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="D42" s="42"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="15">
-        <v>32</v>
-      </c>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="J42" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="K42" s="18"/>
-    </row>
-    <row r="43" spans="1:11" ht="12.5">
-      <c r="A43" s="14">
-        <v>41</v>
-      </c>
-      <c r="B43" s="15">
-        <v>1</v>
-      </c>
-      <c r="C43" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="D43" s="42"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="15">
-        <v>6</v>
-      </c>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="I43" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="J43" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="K43" s="18"/>
-    </row>
-    <row r="44" spans="1:11" ht="12.5">
-      <c r="A44" s="14">
-        <v>42</v>
-      </c>
-      <c r="B44" s="15">
-        <v>1</v>
-      </c>
-      <c r="C44" s="54" t="s">
-        <v>172</v>
-      </c>
-      <c r="D44" s="42"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="15">
-        <v>4</v>
-      </c>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="I44" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="J44" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="K44" s="18"/>
-    </row>
-    <row r="45" spans="1:11" ht="12.5">
-      <c r="A45" s="14">
-        <v>43</v>
-      </c>
-      <c r="B45" s="15">
-        <v>1</v>
-      </c>
-      <c r="C45" s="54" t="s">
-        <v>175</v>
-      </c>
-      <c r="D45" s="42"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="15">
-        <v>4</v>
-      </c>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="I45" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="J45" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="K45" s="18"/>
-    </row>
-    <row r="46" spans="1:11" ht="12.5">
-      <c r="A46" s="14">
-        <v>44</v>
-      </c>
-      <c r="B46" s="15">
-        <v>1</v>
-      </c>
-      <c r="C46" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="D46" s="42"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="15">
-        <v>4</v>
-      </c>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="I46" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="J46" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="K46" s="18"/>
-    </row>
-    <row r="47" spans="1:11" ht="12.5">
-      <c r="A47" s="14">
-        <v>45</v>
-      </c>
-      <c r="B47" s="15">
-        <v>1</v>
-      </c>
-      <c r="C47" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="D47" s="42"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="15">
-        <v>4</v>
-      </c>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="I47" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="J47" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="K47" s="18"/>
-    </row>
-    <row r="48" spans="1:11" ht="12.5">
-      <c r="A48" s="14">
-        <v>46</v>
-      </c>
-      <c r="B48" s="15">
-        <v>1</v>
-      </c>
-      <c r="C48" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="D48" s="42"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="15">
-        <v>4</v>
-      </c>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="I48" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="J48" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="K48" s="18"/>
-    </row>
-    <row r="49" spans="1:11" ht="12.5">
-      <c r="A49" s="14">
-        <v>47</v>
-      </c>
-      <c r="B49" s="15">
-        <v>1</v>
-      </c>
-      <c r="C49" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="D49" s="42"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="15">
-        <v>4</v>
-      </c>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="I49" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="J49" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="K49" s="18"/>
-    </row>
-    <row r="50" spans="1:11" ht="12.5">
-      <c r="A50" s="14">
-        <v>48</v>
-      </c>
-      <c r="B50" s="15">
-        <v>1</v>
-      </c>
-      <c r="C50" s="40" t="s">
-        <v>182</v>
-      </c>
-      <c r="D50" s="42"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="15">
-        <v>1</v>
-      </c>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="I50" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="J50" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="K50" s="18"/>
-    </row>
-    <row r="51" spans="1:11" ht="12.5">
-      <c r="A51" s="14">
-        <v>49</v>
-      </c>
-      <c r="B51" s="15">
-        <v>2</v>
-      </c>
-      <c r="C51" s="15"/>
-      <c r="D51" s="40" t="s">
-        <v>185</v>
-      </c>
-      <c r="E51" s="41"/>
-      <c r="F51" s="15">
-        <v>3</v>
-      </c>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="I51" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="J51" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="K51" s="18"/>
-    </row>
-    <row r="52" spans="1:11" ht="12.5">
-      <c r="A52" s="14">
-        <v>50</v>
-      </c>
-      <c r="B52" s="15">
-        <v>2</v>
-      </c>
-      <c r="C52" s="15"/>
-      <c r="D52" s="40" t="s">
-        <v>189</v>
-      </c>
-      <c r="E52" s="41"/>
-      <c r="F52" s="15">
-        <v>2</v>
-      </c>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="I52" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="J52" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="K52" s="18"/>
-    </row>
-    <row r="53" spans="1:11" ht="12.5">
-      <c r="A53" s="14">
-        <v>51</v>
-      </c>
-      <c r="B53" s="15">
-        <v>2</v>
-      </c>
-      <c r="C53" s="15"/>
-      <c r="D53" s="40" t="s">
-        <v>192</v>
-      </c>
-      <c r="E53" s="41"/>
-      <c r="F53" s="15">
-        <v>1</v>
-      </c>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="I53" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="J53" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="K53" s="18"/>
-    </row>
-    <row r="54" spans="1:11" ht="12.5">
-      <c r="A54" s="14">
-        <v>52</v>
-      </c>
-      <c r="B54" s="15">
-        <v>1</v>
-      </c>
-      <c r="C54" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="D54" s="42"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="15">
-        <v>1</v>
-      </c>
-      <c r="G54" s="15"/>
-      <c r="H54" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
-      <c r="K54" s="18"/>
-    </row>
-    <row r="55" spans="1:11" ht="12.5">
-      <c r="A55" s="14">
-        <v>53</v>
-      </c>
-      <c r="B55" s="15">
-        <v>2</v>
-      </c>
-      <c r="C55" s="15"/>
-      <c r="D55" s="40" t="s">
-        <v>196</v>
-      </c>
-      <c r="E55" s="41"/>
-      <c r="F55" s="15">
-        <v>1</v>
-      </c>
-      <c r="G55" s="15"/>
-      <c r="H55" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="I55" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="J55" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="K55" s="18"/>
-    </row>
-    <row r="56" spans="1:11" ht="12.5">
-      <c r="A56" s="14">
-        <v>54</v>
-      </c>
-      <c r="B56" s="15">
-        <v>2</v>
-      </c>
-      <c r="C56" s="15"/>
-      <c r="D56" s="40" t="s">
-        <v>185</v>
-      </c>
-      <c r="E56" s="41"/>
-      <c r="F56" s="15">
-        <v>1</v>
-      </c>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="I56" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="J56" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="K56" s="18"/>
-    </row>
-    <row r="57" spans="1:11" ht="12.5">
-      <c r="A57" s="14">
-        <v>55</v>
-      </c>
-      <c r="B57" s="15">
-        <v>2</v>
-      </c>
-      <c r="C57" s="15"/>
-      <c r="D57" s="40" t="s">
-        <v>197</v>
-      </c>
-      <c r="E57" s="41"/>
-      <c r="F57" s="15">
-        <v>1</v>
-      </c>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="I57" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="J57" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="K57" s="18"/>
-    </row>
-    <row r="58" spans="1:11" ht="12.5">
-      <c r="A58" s="14">
-        <v>56</v>
-      </c>
-      <c r="B58" s="15">
-        <v>1</v>
-      </c>
-      <c r="C58" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="D58" s="42"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="15">
-        <v>1</v>
-      </c>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="I58" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="J58" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="K58" s="18"/>
-    </row>
-    <row r="59" spans="1:11" ht="12.5">
-      <c r="A59" s="14">
-        <v>57</v>
-      </c>
-      <c r="B59" s="15">
-        <v>1</v>
-      </c>
-      <c r="C59" s="40" t="s">
-        <v>203</v>
-      </c>
-      <c r="D59" s="42"/>
-      <c r="E59" s="41"/>
-      <c r="F59" s="15">
-        <v>1</v>
-      </c>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="I59" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="J59" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="K59" s="18"/>
-    </row>
-    <row r="60" spans="1:11" ht="12.5">
-      <c r="A60" s="14">
-        <v>58</v>
-      </c>
-      <c r="B60" s="15">
-        <v>2</v>
-      </c>
-      <c r="C60" s="15"/>
-      <c r="D60" s="40" t="s">
-        <v>205</v>
-      </c>
-      <c r="E60" s="41"/>
-      <c r="F60" s="15">
-        <v>1</v>
-      </c>
-      <c r="G60" s="15"/>
-      <c r="H60" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="I60" s="15"/>
-      <c r="J60" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="K60" s="18"/>
-    </row>
-    <row r="61" spans="1:11" ht="12.5">
-      <c r="A61" s="14">
-        <v>59</v>
-      </c>
-      <c r="B61" s="15">
-        <v>2</v>
-      </c>
-      <c r="C61" s="15"/>
-      <c r="D61" s="40" t="s">
-        <v>185</v>
-      </c>
-      <c r="E61" s="41"/>
-      <c r="F61" s="15">
-        <v>1</v>
-      </c>
-      <c r="G61" s="15"/>
-      <c r="H61" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="I61" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="J61" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="K61" s="18"/>
-    </row>
-    <row r="62" spans="1:11" ht="12.5">
-      <c r="A62" s="14">
-        <v>60</v>
-      </c>
-      <c r="B62" s="15">
-        <v>2</v>
-      </c>
-      <c r="C62" s="15"/>
-      <c r="D62" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="E62" s="41"/>
-      <c r="F62" s="15">
-        <v>1</v>
-      </c>
-      <c r="G62" s="15"/>
-      <c r="H62" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="I62" s="15"/>
-      <c r="J62" s="15"/>
-      <c r="K62" s="18"/>
-    </row>
-    <row r="63" spans="1:11" ht="12.5">
-      <c r="A63" s="14">
-        <v>61</v>
-      </c>
-      <c r="B63" s="15">
-        <v>3</v>
-      </c>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="F63" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="G63" s="15"/>
-      <c r="H63" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="I63" s="15"/>
-      <c r="J63" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="K63" s="18" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="12.5">
-      <c r="A64" s="14">
-        <v>62</v>
-      </c>
-      <c r="B64" s="15">
-        <v>3</v>
-      </c>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="F64" s="15">
-        <v>1</v>
-      </c>
-      <c r="G64" s="15"/>
-      <c r="H64" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="I64" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="J64" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="K64" s="18"/>
-    </row>
-    <row r="65" spans="1:11" ht="12.5">
-      <c r="A65" s="14">
-        <v>63</v>
-      </c>
-      <c r="B65" s="15">
-        <v>1</v>
-      </c>
-      <c r="C65" s="40" t="s">
-        <v>212</v>
-      </c>
-      <c r="D65" s="42"/>
-      <c r="E65" s="41"/>
-      <c r="F65" s="15">
-        <v>1</v>
-      </c>
-      <c r="G65" s="15"/>
-      <c r="H65" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="I65" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="J65" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="K65" s="18"/>
-    </row>
-    <row r="66" spans="1:11" ht="12.5">
-      <c r="A66" s="14">
-        <v>64</v>
-      </c>
-      <c r="B66" s="15">
-        <v>1</v>
-      </c>
-      <c r="C66" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="D66" s="42"/>
-      <c r="E66" s="41"/>
-      <c r="F66" s="15">
-        <v>1</v>
-      </c>
-      <c r="G66" s="15"/>
-      <c r="H66" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="I66" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="J66" s="22" t="s">
+      <c r="B67" s="32">
+        <v>1</v>
+      </c>
+      <c r="C67" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="K66" s="18"/>
-    </row>
-    <row r="67" spans="1:11" ht="12.5">
-      <c r="A67" s="14">
-        <v>65</v>
-      </c>
-      <c r="B67" s="15">
-        <v>1</v>
-      </c>
-      <c r="C67" s="40" t="s">
+      <c r="D67" s="39"/>
+      <c r="E67" s="40"/>
+      <c r="F67" s="33">
+        <v>1</v>
+      </c>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="D67" s="42"/>
-      <c r="E67" s="41"/>
-      <c r="F67" s="15">
-        <v>1</v>
-      </c>
-      <c r="G67" s="15"/>
-      <c r="H67" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="I67" s="15" t="s">
+      <c r="I67" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="J67" s="22" t="s">
+      <c r="J67" s="34" t="s">
         <v>221</v>
       </c>
-      <c r="K67" s="18"/>
+      <c r="K67" s="53" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="68" spans="1:11" ht="12.5">
-      <c r="A68" s="32">
-        <v>66</v>
-      </c>
-      <c r="B68" s="36">
-        <v>1</v>
-      </c>
-      <c r="C68" s="43" t="s">
-        <v>222</v>
-      </c>
-      <c r="D68" s="44"/>
-      <c r="E68" s="45"/>
-      <c r="F68" s="37">
-        <v>1</v>
-      </c>
-      <c r="G68" s="36"/>
-      <c r="H68" s="36" t="s">
-        <v>223</v>
-      </c>
-      <c r="I68" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="J68" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="K68" s="39"/>
+      <c r="J68" s="28"/>
     </row>
     <row r="69" spans="1:11" ht="12.5">
-      <c r="J69" s="30"/>
+      <c r="J69" s="28"/>
     </row>
     <row r="70" spans="1:11" ht="12.5">
-      <c r="J70" s="30"/>
+      <c r="J70" s="28"/>
     </row>
     <row r="71" spans="1:11" ht="12.5">
-      <c r="J71" s="30"/>
+      <c r="J71" s="28"/>
     </row>
     <row r="72" spans="1:11" ht="12.5">
-      <c r="J72" s="30"/>
+      <c r="J72" s="28"/>
     </row>
     <row r="73" spans="1:11" ht="12.5">
-      <c r="J73" s="30"/>
+      <c r="J73" s="28"/>
     </row>
     <row r="74" spans="1:11" ht="12.5">
-      <c r="J74" s="30"/>
+      <c r="J74" s="28"/>
     </row>
     <row r="75" spans="1:11" ht="12.5">
-      <c r="J75" s="30"/>
+      <c r="J75" s="28"/>
     </row>
     <row r="76" spans="1:11" ht="12.5">
-      <c r="J76" s="30"/>
+      <c r="J76" s="28"/>
     </row>
     <row r="77" spans="1:11" ht="12.5">
-      <c r="J77" s="30"/>
+      <c r="J77" s="28"/>
     </row>
     <row r="78" spans="1:11" ht="12.5">
-      <c r="J78" s="30"/>
+      <c r="J78" s="28"/>
     </row>
     <row r="79" spans="1:11" ht="12.5">
-      <c r="J79" s="30"/>
+      <c r="J79" s="28"/>
     </row>
     <row r="80" spans="1:11" ht="12.5">
-      <c r="J80" s="30"/>
+      <c r="J80" s="28"/>
     </row>
     <row r="81" spans="10:10" ht="12.5">
-      <c r="J81" s="30"/>
+      <c r="J81" s="28"/>
     </row>
     <row r="82" spans="10:10" ht="12.5">
-      <c r="J82" s="30"/>
+      <c r="J82" s="28"/>
     </row>
     <row r="83" spans="10:10" ht="12.5">
-      <c r="J83" s="30"/>
+      <c r="J83" s="28"/>
     </row>
     <row r="84" spans="10:10" ht="12.5">
-      <c r="J84" s="30"/>
+      <c r="J84" s="28"/>
     </row>
     <row r="85" spans="10:10" ht="12.5">
-      <c r="J85" s="30"/>
+      <c r="J85" s="28"/>
     </row>
     <row r="86" spans="10:10" ht="12.5">
-      <c r="J86" s="30"/>
+      <c r="J86" s="28"/>
     </row>
     <row r="87" spans="10:10" ht="12.5">
-      <c r="J87" s="30"/>
+      <c r="J87" s="28"/>
     </row>
     <row r="88" spans="10:10" ht="12.5">
-      <c r="J88" s="30"/>
+      <c r="J88" s="28"/>
     </row>
     <row r="89" spans="10:10" ht="12.5">
-      <c r="J89" s="30"/>
+      <c r="J89" s="28"/>
     </row>
     <row r="90" spans="10:10" ht="12.5">
-      <c r="J90" s="30"/>
+      <c r="J90" s="28"/>
     </row>
     <row r="91" spans="10:10" ht="12.5">
-      <c r="J91" s="30"/>
+      <c r="J91" s="28"/>
     </row>
     <row r="92" spans="10:10" ht="12.5">
-      <c r="J92" s="30"/>
+      <c r="J92" s="28"/>
     </row>
     <row r="93" spans="10:10" ht="12.5">
-      <c r="J93" s="30"/>
+      <c r="J93" s="28"/>
     </row>
     <row r="94" spans="10:10" ht="12.5">
-      <c r="J94" s="30"/>
+      <c r="J94" s="28"/>
     </row>
     <row r="95" spans="10:10" ht="12.5">
-      <c r="J95" s="30"/>
+      <c r="J95" s="28"/>
     </row>
     <row r="96" spans="10:10" ht="12.5">
-      <c r="J96" s="30"/>
+      <c r="J96" s="28"/>
     </row>
     <row r="97" spans="10:10" ht="12.5">
-      <c r="J97" s="30"/>
+      <c r="J97" s="28"/>
     </row>
     <row r="98" spans="10:10" ht="12.5">
-      <c r="J98" s="30"/>
+      <c r="J98" s="28"/>
     </row>
     <row r="99" spans="10:10" ht="12.5">
-      <c r="J99" s="30"/>
+      <c r="J99" s="28"/>
     </row>
     <row r="100" spans="10:10" ht="12.5">
-      <c r="J100" s="30"/>
+      <c r="J100" s="28"/>
     </row>
     <row r="101" spans="10:10" ht="12.5">
-      <c r="J101" s="30"/>
+      <c r="J101" s="28"/>
     </row>
     <row r="102" spans="10:10" ht="12.5">
-      <c r="J102" s="30"/>
+      <c r="J102" s="28"/>
     </row>
     <row r="103" spans="10:10" ht="12.5">
-      <c r="J103" s="30"/>
+      <c r="J103" s="28"/>
     </row>
     <row r="104" spans="10:10" ht="12.5">
-      <c r="J104" s="30"/>
+      <c r="J104" s="28"/>
     </row>
     <row r="105" spans="10:10" ht="12.5">
-      <c r="J105" s="30"/>
+      <c r="J105" s="28"/>
     </row>
     <row r="106" spans="10:10" ht="12.5">
-      <c r="J106" s="30"/>
+      <c r="J106" s="28"/>
     </row>
     <row r="107" spans="10:10" ht="12.5">
-      <c r="J107" s="30"/>
+      <c r="J107" s="28"/>
     </row>
     <row r="108" spans="10:10" ht="12.5">
-      <c r="J108" s="30"/>
+      <c r="J108" s="28"/>
     </row>
     <row r="109" spans="10:10" ht="12.5">
-      <c r="J109" s="30"/>
+      <c r="J109" s="28"/>
     </row>
     <row r="110" spans="10:10" ht="12.5">
-      <c r="J110" s="30"/>
+      <c r="J110" s="28"/>
     </row>
     <row r="111" spans="10:10" ht="12.5">
-      <c r="J111" s="30"/>
+      <c r="J111" s="28"/>
     </row>
     <row r="112" spans="10:10" ht="12.5">
-      <c r="J112" s="30"/>
+      <c r="J112" s="28"/>
     </row>
     <row r="113" spans="10:10" ht="12.5">
-      <c r="J113" s="30"/>
+      <c r="J113" s="28"/>
     </row>
     <row r="114" spans="10:10" ht="12.5">
-      <c r="J114" s="30"/>
+      <c r="J114" s="28"/>
     </row>
     <row r="115" spans="10:10" ht="12.5">
-      <c r="J115" s="30"/>
+      <c r="J115" s="28"/>
     </row>
     <row r="116" spans="10:10" ht="12.5">
-      <c r="J116" s="30"/>
+      <c r="J116" s="28"/>
     </row>
     <row r="117" spans="10:10" ht="12.5">
-      <c r="J117" s="30"/>
+      <c r="J117" s="28"/>
     </row>
     <row r="118" spans="10:10" ht="12.5">
-      <c r="J118" s="30"/>
+      <c r="J118" s="28"/>
     </row>
     <row r="119" spans="10:10" ht="12.5">
-      <c r="J119" s="30"/>
+      <c r="J119" s="28"/>
     </row>
     <row r="120" spans="10:10" ht="12.5">
-      <c r="J120" s="30"/>
+      <c r="J120" s="28"/>
     </row>
     <row r="121" spans="10:10" ht="12.5">
-      <c r="J121" s="30"/>
+      <c r="J121" s="28"/>
     </row>
     <row r="122" spans="10:10" ht="12.5">
-      <c r="J122" s="30"/>
+      <c r="J122" s="28"/>
     </row>
     <row r="123" spans="10:10" ht="12.5">
-      <c r="J123" s="30"/>
+      <c r="J123" s="28"/>
     </row>
     <row r="124" spans="10:10" ht="12.5">
-      <c r="J124" s="30"/>
+      <c r="J124" s="28"/>
     </row>
     <row r="125" spans="10:10" ht="12.5">
-      <c r="J125" s="30"/>
+      <c r="J125" s="28"/>
     </row>
     <row r="126" spans="10:10" ht="12.5">
-      <c r="J126" s="30"/>
+      <c r="J126" s="28"/>
     </row>
     <row r="127" spans="10:10" ht="12.5">
-      <c r="J127" s="30"/>
+      <c r="J127" s="28"/>
     </row>
     <row r="128" spans="10:10" ht="12.5">
-      <c r="J128" s="30"/>
+      <c r="J128" s="28"/>
     </row>
     <row r="129" spans="10:10" ht="12.5">
-      <c r="J129" s="30"/>
+      <c r="J129" s="28"/>
     </row>
     <row r="130" spans="10:10" ht="12.5">
-      <c r="J130" s="30"/>
+      <c r="J130" s="28"/>
     </row>
     <row r="131" spans="10:10" ht="12.5">
-      <c r="J131" s="30"/>
+      <c r="J131" s="28"/>
     </row>
     <row r="132" spans="10:10" ht="12.5">
-      <c r="J132" s="30"/>
+      <c r="J132" s="28"/>
     </row>
     <row r="133" spans="10:10" ht="12.5">
-      <c r="J133" s="30"/>
+      <c r="J133" s="28"/>
     </row>
     <row r="134" spans="10:10" ht="12.5">
-      <c r="J134" s="30"/>
+      <c r="J134" s="28"/>
     </row>
     <row r="135" spans="10:10" ht="12.5">
-      <c r="J135" s="30"/>
+      <c r="J135" s="28"/>
     </row>
     <row r="136" spans="10:10" ht="12.5">
-      <c r="J136" s="30"/>
+      <c r="J136" s="28"/>
     </row>
     <row r="137" spans="10:10" ht="12.5">
-      <c r="J137" s="30"/>
+      <c r="J137" s="28"/>
     </row>
     <row r="138" spans="10:10" ht="12.5">
-      <c r="J138" s="30"/>
+      <c r="J138" s="28"/>
     </row>
     <row r="139" spans="10:10" ht="12.5">
-      <c r="J139" s="30"/>
+      <c r="J139" s="28"/>
     </row>
     <row r="140" spans="10:10" ht="12.5">
-      <c r="J140" s="30"/>
+      <c r="J140" s="28"/>
     </row>
     <row r="141" spans="10:10" ht="12.5">
-      <c r="J141" s="30"/>
+      <c r="J141" s="28"/>
     </row>
     <row r="142" spans="10:10" ht="12.5">
-      <c r="J142" s="30"/>
+      <c r="J142" s="28"/>
     </row>
     <row r="143" spans="10:10" ht="12.5">
-      <c r="J143" s="30"/>
+      <c r="J143" s="28"/>
     </row>
     <row r="144" spans="10:10" ht="12.5">
-      <c r="J144" s="30"/>
+      <c r="J144" s="28"/>
     </row>
     <row r="145" spans="10:10" ht="12.5">
-      <c r="J145" s="30"/>
+      <c r="J145" s="28"/>
     </row>
     <row r="146" spans="10:10" ht="12.5">
-      <c r="J146" s="30"/>
+      <c r="J146" s="28"/>
     </row>
     <row r="147" spans="10:10" ht="12.5">
-      <c r="J147" s="30"/>
+      <c r="J147" s="28"/>
     </row>
     <row r="148" spans="10:10" ht="12.5">
-      <c r="J148" s="30"/>
+      <c r="J148" s="28"/>
     </row>
     <row r="149" spans="10:10" ht="12.5">
-      <c r="J149" s="30"/>
+      <c r="J149" s="28"/>
     </row>
     <row r="150" spans="10:10" ht="12.5">
-      <c r="J150" s="30"/>
+      <c r="J150" s="28"/>
     </row>
     <row r="151" spans="10:10" ht="12.5">
-      <c r="J151" s="30"/>
+      <c r="J151" s="28"/>
     </row>
     <row r="152" spans="10:10" ht="12.5">
-      <c r="J152" s="30"/>
+      <c r="J152" s="28"/>
     </row>
     <row r="153" spans="10:10" ht="12.5">
-      <c r="J153" s="30"/>
+      <c r="J153" s="28"/>
     </row>
     <row r="154" spans="10:10" ht="12.5">
-      <c r="J154" s="30"/>
+      <c r="J154" s="28"/>
     </row>
     <row r="155" spans="10:10" ht="12.5">
-      <c r="J155" s="30"/>
+      <c r="J155" s="28"/>
     </row>
     <row r="156" spans="10:10" ht="12.5">
-      <c r="J156" s="30"/>
+      <c r="J156" s="28"/>
     </row>
     <row r="157" spans="10:10" ht="12.5">
-      <c r="J157" s="30"/>
+      <c r="J157" s="28"/>
     </row>
     <row r="158" spans="10:10" ht="12.5">
-      <c r="J158" s="30"/>
+      <c r="J158" s="28"/>
     </row>
     <row r="159" spans="10:10" ht="12.5">
-      <c r="J159" s="30"/>
+      <c r="J159" s="28"/>
     </row>
     <row r="160" spans="10:10" ht="12.5">
-      <c r="J160" s="30"/>
+      <c r="J160" s="28"/>
     </row>
     <row r="161" spans="10:10" ht="12.5">
-      <c r="J161" s="30"/>
+      <c r="J161" s="28"/>
     </row>
     <row r="162" spans="10:10" ht="12.5">
-      <c r="J162" s="30"/>
+      <c r="J162" s="28"/>
     </row>
     <row r="163" spans="10:10" ht="12.5">
-      <c r="J163" s="30"/>
+      <c r="J163" s="28"/>
     </row>
     <row r="164" spans="10:10" ht="12.5">
-      <c r="J164" s="30"/>
+      <c r="J164" s="28"/>
     </row>
     <row r="165" spans="10:10" ht="12.5">
-      <c r="J165" s="30"/>
+      <c r="J165" s="28"/>
     </row>
     <row r="166" spans="10:10" ht="12.5">
-      <c r="J166" s="30"/>
+      <c r="J166" s="28"/>
     </row>
     <row r="167" spans="10:10" ht="12.5">
-      <c r="J167" s="30"/>
+      <c r="J167" s="28"/>
     </row>
     <row r="168" spans="10:10" ht="12.5">
-      <c r="J168" s="30"/>
+      <c r="J168" s="28"/>
     </row>
     <row r="169" spans="10:10" ht="12.5">
-      <c r="J169" s="30"/>
+      <c r="J169" s="28"/>
     </row>
     <row r="170" spans="10:10" ht="12.5">
-      <c r="J170" s="30"/>
+      <c r="J170" s="28"/>
     </row>
     <row r="171" spans="10:10" ht="12.5">
-      <c r="J171" s="30"/>
+      <c r="J171" s="28"/>
     </row>
     <row r="172" spans="10:10" ht="12.5">
-      <c r="J172" s="30"/>
+      <c r="J172" s="28"/>
     </row>
     <row r="173" spans="10:10" ht="12.5">
-      <c r="J173" s="30"/>
+      <c r="J173" s="28"/>
     </row>
     <row r="174" spans="10:10" ht="12.5">
-      <c r="J174" s="30"/>
+      <c r="J174" s="28"/>
     </row>
     <row r="175" spans="10:10" ht="12.5">
-      <c r="J175" s="30"/>
+      <c r="J175" s="28"/>
     </row>
     <row r="176" spans="10:10" ht="12.5">
-      <c r="J176" s="30"/>
+      <c r="J176" s="28"/>
     </row>
     <row r="177" spans="10:10" ht="12.5">
-      <c r="J177" s="30"/>
+      <c r="J177" s="28"/>
     </row>
     <row r="178" spans="10:10" ht="12.5">
-      <c r="J178" s="30"/>
+      <c r="J178" s="28"/>
     </row>
     <row r="179" spans="10:10" ht="12.5">
-      <c r="J179" s="30"/>
+      <c r="J179" s="28"/>
     </row>
     <row r="180" spans="10:10" ht="12.5">
-      <c r="J180" s="30"/>
+      <c r="J180" s="28"/>
     </row>
     <row r="181" spans="10:10" ht="12.5">
-      <c r="J181" s="30"/>
+      <c r="J181" s="28"/>
     </row>
     <row r="182" spans="10:10" ht="12.5">
-      <c r="J182" s="30"/>
+      <c r="J182" s="28"/>
     </row>
     <row r="183" spans="10:10" ht="12.5">
-      <c r="J183" s="30"/>
+      <c r="J183" s="28"/>
     </row>
     <row r="184" spans="10:10" ht="12.5">
-      <c r="J184" s="30"/>
+      <c r="J184" s="28"/>
     </row>
     <row r="185" spans="10:10" ht="12.5">
-      <c r="J185" s="30"/>
+      <c r="J185" s="28"/>
     </row>
     <row r="186" spans="10:10" ht="12.5">
-      <c r="J186" s="30"/>
+      <c r="J186" s="28"/>
     </row>
     <row r="187" spans="10:10" ht="12.5">
-      <c r="J187" s="30"/>
+      <c r="J187" s="28"/>
     </row>
     <row r="188" spans="10:10" ht="12.5">
-      <c r="J188" s="30"/>
+      <c r="J188" s="28"/>
     </row>
     <row r="189" spans="10:10" ht="12.5">
-      <c r="J189" s="30"/>
+      <c r="J189" s="28"/>
     </row>
     <row r="190" spans="10:10" ht="12.5">
-      <c r="J190" s="30"/>
+      <c r="J190" s="28"/>
     </row>
     <row r="191" spans="10:10" ht="12.5">
-      <c r="J191" s="30"/>
+      <c r="J191" s="28"/>
     </row>
     <row r="192" spans="10:10" ht="12.5">
-      <c r="J192" s="30"/>
+      <c r="J192" s="28"/>
     </row>
     <row r="193" spans="10:10" ht="12.5">
-      <c r="J193" s="30"/>
+      <c r="J193" s="28"/>
     </row>
     <row r="194" spans="10:10" ht="12.5">
-      <c r="J194" s="30"/>
+      <c r="J194" s="28"/>
     </row>
     <row r="195" spans="10:10" ht="12.5">
-      <c r="J195" s="30"/>
+      <c r="J195" s="28"/>
     </row>
     <row r="196" spans="10:10" ht="12.5">
-      <c r="J196" s="30"/>
+      <c r="J196" s="28"/>
     </row>
     <row r="197" spans="10:10" ht="12.5">
-      <c r="J197" s="30"/>
+      <c r="J197" s="28"/>
     </row>
     <row r="198" spans="10:10" ht="12.5">
-      <c r="J198" s="30"/>
+      <c r="J198" s="28"/>
     </row>
     <row r="199" spans="10:10" ht="12.5">
-      <c r="J199" s="30"/>
+      <c r="J199" s="28"/>
     </row>
     <row r="200" spans="10:10" ht="12.5">
-      <c r="J200" s="30"/>
+      <c r="J200" s="28"/>
     </row>
     <row r="201" spans="10:10" ht="12.5">
-      <c r="J201" s="30"/>
+      <c r="J201" s="28"/>
     </row>
     <row r="202" spans="10:10" ht="12.5">
-      <c r="J202" s="30"/>
+      <c r="J202" s="28"/>
     </row>
     <row r="203" spans="10:10" ht="12.5">
-      <c r="J203" s="30"/>
+      <c r="J203" s="28"/>
     </row>
     <row r="204" spans="10:10" ht="12.5">
-      <c r="J204" s="30"/>
+      <c r="J204" s="28"/>
     </row>
     <row r="205" spans="10:10" ht="12.5">
-      <c r="J205" s="30"/>
+      <c r="J205" s="28"/>
     </row>
     <row r="206" spans="10:10" ht="12.5">
-      <c r="J206" s="30"/>
+      <c r="J206" s="28"/>
     </row>
     <row r="207" spans="10:10" ht="12.5">
-      <c r="J207" s="30"/>
+      <c r="J207" s="28"/>
     </row>
     <row r="208" spans="10:10" ht="12.5">
-      <c r="J208" s="30"/>
+      <c r="J208" s="28"/>
     </row>
     <row r="209" spans="10:10" ht="12.5">
-      <c r="J209" s="30"/>
+      <c r="J209" s="28"/>
     </row>
     <row r="210" spans="10:10" ht="12.5">
-      <c r="J210" s="30"/>
+      <c r="J210" s="28"/>
     </row>
     <row r="211" spans="10:10" ht="12.5">
-      <c r="J211" s="30"/>
+      <c r="J211" s="28"/>
     </row>
     <row r="212" spans="10:10" ht="12.5">
-      <c r="J212" s="30"/>
+      <c r="J212" s="28"/>
     </row>
     <row r="213" spans="10:10" ht="12.5">
-      <c r="J213" s="30"/>
+      <c r="J213" s="28"/>
     </row>
     <row r="214" spans="10:10" ht="12.5">
-      <c r="J214" s="30"/>
+      <c r="J214" s="28"/>
     </row>
     <row r="215" spans="10:10" ht="12.5">
-      <c r="J215" s="30"/>
+      <c r="J215" s="28"/>
     </row>
     <row r="216" spans="10:10" ht="12.5">
-      <c r="J216" s="30"/>
+      <c r="J216" s="28"/>
     </row>
     <row r="217" spans="10:10" ht="12.5">
-      <c r="J217" s="30"/>
+      <c r="J217" s="28"/>
     </row>
     <row r="218" spans="10:10" ht="12.5">
-      <c r="J218" s="30"/>
+      <c r="J218" s="28"/>
     </row>
     <row r="219" spans="10:10" ht="12.5">
-      <c r="J219" s="30"/>
+      <c r="J219" s="28"/>
     </row>
     <row r="220" spans="10:10" ht="12.5">
-      <c r="J220" s="30"/>
+      <c r="J220" s="28"/>
     </row>
     <row r="221" spans="10:10" ht="12.5">
-      <c r="J221" s="30"/>
+      <c r="J221" s="28"/>
     </row>
     <row r="222" spans="10:10" ht="12.5">
-      <c r="J222" s="30"/>
+      <c r="J222" s="28"/>
     </row>
     <row r="223" spans="10:10" ht="12.5">
-      <c r="J223" s="30"/>
+      <c r="J223" s="28"/>
     </row>
     <row r="224" spans="10:10" ht="12.5">
-      <c r="J224" s="30"/>
+      <c r="J224" s="28"/>
     </row>
     <row r="225" spans="10:10" ht="12.5">
-      <c r="J225" s="30"/>
+      <c r="J225" s="28"/>
     </row>
     <row r="226" spans="10:10" ht="12.5">
-      <c r="J226" s="30"/>
+      <c r="J226" s="28"/>
     </row>
     <row r="227" spans="10:10" ht="12.5">
-      <c r="J227" s="30"/>
+      <c r="J227" s="28"/>
     </row>
     <row r="228" spans="10:10" ht="12.5">
-      <c r="J228" s="30"/>
+      <c r="J228" s="28"/>
     </row>
     <row r="229" spans="10:10" ht="12.5">
-      <c r="J229" s="30"/>
+      <c r="J229" s="28"/>
     </row>
     <row r="230" spans="10:10" ht="12.5">
-      <c r="J230" s="30"/>
+      <c r="J230" s="28"/>
     </row>
     <row r="231" spans="10:10" ht="12.5">
-      <c r="J231" s="30"/>
+      <c r="J231" s="28"/>
     </row>
     <row r="232" spans="10:10" ht="12.5">
-      <c r="J232" s="30"/>
+      <c r="J232" s="28"/>
     </row>
     <row r="233" spans="10:10" ht="12.5">
-      <c r="J233" s="30"/>
+      <c r="J233" s="28"/>
     </row>
     <row r="234" spans="10:10" ht="12.5">
-      <c r="J234" s="30"/>
+      <c r="J234" s="28"/>
     </row>
     <row r="235" spans="10:10" ht="12.5">
-      <c r="J235" s="30"/>
+      <c r="J235" s="28"/>
     </row>
     <row r="236" spans="10:10" ht="12.5">
-      <c r="J236" s="30"/>
+      <c r="J236" s="28"/>
     </row>
     <row r="237" spans="10:10" ht="12.5">
-      <c r="J237" s="30"/>
+      <c r="J237" s="28"/>
     </row>
     <row r="238" spans="10:10" ht="12.5">
-      <c r="J238" s="30"/>
+      <c r="J238" s="28"/>
     </row>
     <row r="239" spans="10:10" ht="12.5">
-      <c r="J239" s="30"/>
+      <c r="J239" s="28"/>
     </row>
     <row r="240" spans="10:10" ht="12.5">
-      <c r="J240" s="30"/>
+      <c r="J240" s="28"/>
     </row>
     <row r="241" spans="10:10" ht="12.5">
-      <c r="J241" s="30"/>
+      <c r="J241" s="28"/>
     </row>
     <row r="242" spans="10:10" ht="12.5">
-      <c r="J242" s="30"/>
+      <c r="J242" s="28"/>
     </row>
     <row r="243" spans="10:10" ht="12.5">
-      <c r="J243" s="30"/>
+      <c r="J243" s="28"/>
     </row>
     <row r="244" spans="10:10" ht="12.5">
-      <c r="J244" s="30"/>
+      <c r="J244" s="28"/>
     </row>
     <row r="245" spans="10:10" ht="12.5">
-      <c r="J245" s="30"/>
+      <c r="J245" s="28"/>
     </row>
     <row r="246" spans="10:10" ht="12.5">
-      <c r="J246" s="30"/>
+      <c r="J246" s="28"/>
     </row>
     <row r="247" spans="10:10" ht="12.5">
-      <c r="J247" s="30"/>
+      <c r="J247" s="28"/>
     </row>
     <row r="248" spans="10:10" ht="12.5">
-      <c r="J248" s="30"/>
+      <c r="J248" s="28"/>
     </row>
     <row r="249" spans="10:10" ht="12.5">
-      <c r="J249" s="30"/>
+      <c r="J249" s="28"/>
     </row>
     <row r="250" spans="10:10" ht="12.5">
-      <c r="J250" s="30"/>
+      <c r="J250" s="28"/>
     </row>
     <row r="251" spans="10:10" ht="12.5">
-      <c r="J251" s="30"/>
+      <c r="J251" s="28"/>
     </row>
     <row r="252" spans="10:10" ht="12.5">
-      <c r="J252" s="30"/>
+      <c r="J252" s="28"/>
     </row>
     <row r="253" spans="10:10" ht="12.5">
-      <c r="J253" s="30"/>
+      <c r="J253" s="28"/>
     </row>
     <row r="254" spans="10:10" ht="12.5">
-      <c r="J254" s="30"/>
+      <c r="J254" s="28"/>
     </row>
     <row r="255" spans="10:10" ht="12.5">
-      <c r="J255" s="30"/>
+      <c r="J255" s="28"/>
     </row>
     <row r="256" spans="10:10" ht="12.5">
-      <c r="J256" s="30"/>
+      <c r="J256" s="28"/>
     </row>
     <row r="257" spans="10:10" ht="12.5">
-      <c r="J257" s="30"/>
+      <c r="J257" s="28"/>
     </row>
     <row r="258" spans="10:10" ht="12.5">
-      <c r="J258" s="30"/>
+      <c r="J258" s="28"/>
     </row>
     <row r="259" spans="10:10" ht="12.5">
-      <c r="J259" s="30"/>
+      <c r="J259" s="28"/>
     </row>
     <row r="260" spans="10:10" ht="12.5">
-      <c r="J260" s="30"/>
+      <c r="J260" s="28"/>
     </row>
     <row r="261" spans="10:10" ht="12.5">
-      <c r="J261" s="30"/>
+      <c r="J261" s="28"/>
     </row>
     <row r="262" spans="10:10" ht="12.5">
-      <c r="J262" s="30"/>
+      <c r="J262" s="28"/>
     </row>
     <row r="263" spans="10:10" ht="12.5">
-      <c r="J263" s="30"/>
+      <c r="J263" s="28"/>
     </row>
     <row r="264" spans="10:10" ht="12.5">
-      <c r="J264" s="30"/>
+      <c r="J264" s="28"/>
     </row>
     <row r="265" spans="10:10" ht="12.5">
-      <c r="J265" s="30"/>
+      <c r="J265" s="28"/>
     </row>
     <row r="266" spans="10:10" ht="12.5">
-      <c r="J266" s="30"/>
+      <c r="J266" s="28"/>
     </row>
     <row r="267" spans="10:10" ht="12.5">
-      <c r="J267" s="30"/>
+      <c r="J267" s="28"/>
     </row>
     <row r="268" spans="10:10" ht="12.5">
-      <c r="J268" s="30"/>
+      <c r="J268" s="28"/>
     </row>
     <row r="269" spans="10:10" ht="12.5">
-      <c r="J269" s="30"/>
+      <c r="J269" s="28"/>
     </row>
     <row r="270" spans="10:10" ht="12.5">
-      <c r="J270" s="30"/>
+      <c r="J270" s="28"/>
     </row>
     <row r="271" spans="10:10" ht="12.5">
-      <c r="J271" s="30"/>
+      <c r="J271" s="28"/>
     </row>
     <row r="272" spans="10:10" ht="12.5">
-      <c r="J272" s="30"/>
+      <c r="J272" s="28"/>
     </row>
     <row r="273" spans="10:10" ht="12.5">
-      <c r="J273" s="30"/>
+      <c r="J273" s="28"/>
     </row>
     <row r="274" spans="10:10" ht="12.5">
-      <c r="J274" s="30"/>
+      <c r="J274" s="28"/>
     </row>
     <row r="275" spans="10:10" ht="12.5">
-      <c r="J275" s="30"/>
+      <c r="J275" s="28"/>
     </row>
     <row r="276" spans="10:10" ht="12.5">
-      <c r="J276" s="30"/>
+      <c r="J276" s="28"/>
     </row>
     <row r="277" spans="10:10" ht="12.5">
-      <c r="J277" s="30"/>
+      <c r="J277" s="28"/>
     </row>
     <row r="278" spans="10:10" ht="12.5">
-      <c r="J278" s="30"/>
+      <c r="J278" s="28"/>
     </row>
     <row r="279" spans="10:10" ht="12.5">
-      <c r="J279" s="30"/>
+      <c r="J279" s="28"/>
     </row>
     <row r="280" spans="10:10" ht="12.5">
-      <c r="J280" s="30"/>
+      <c r="J280" s="28"/>
     </row>
     <row r="281" spans="10:10" ht="12.5">
-      <c r="J281" s="30"/>
+      <c r="J281" s="28"/>
     </row>
     <row r="282" spans="10:10" ht="12.5">
-      <c r="J282" s="30"/>
+      <c r="J282" s="28"/>
     </row>
     <row r="283" spans="10:10" ht="12.5">
-      <c r="J283" s="30"/>
+      <c r="J283" s="28"/>
     </row>
     <row r="284" spans="10:10" ht="12.5">
-      <c r="J284" s="30"/>
+      <c r="J284" s="28"/>
     </row>
     <row r="285" spans="10:10" ht="12.5">
-      <c r="J285" s="30"/>
+      <c r="J285" s="28"/>
     </row>
     <row r="286" spans="10:10" ht="12.5">
-      <c r="J286" s="30"/>
+      <c r="J286" s="28"/>
     </row>
     <row r="287" spans="10:10" ht="12.5">
-      <c r="J287" s="30"/>
+      <c r="J287" s="28"/>
     </row>
     <row r="288" spans="10:10" ht="12.5">
-      <c r="J288" s="30"/>
+      <c r="J288" s="28"/>
     </row>
     <row r="289" spans="10:10" ht="12.5">
-      <c r="J289" s="30"/>
+      <c r="J289" s="28"/>
     </row>
     <row r="290" spans="10:10" ht="12.5">
-      <c r="J290" s="30"/>
+      <c r="J290" s="28"/>
     </row>
     <row r="291" spans="10:10" ht="12.5">
-      <c r="J291" s="30"/>
+      <c r="J291" s="28"/>
     </row>
     <row r="292" spans="10:10" ht="12.5">
-      <c r="J292" s="30"/>
+      <c r="J292" s="28"/>
     </row>
     <row r="293" spans="10:10" ht="12.5">
-      <c r="J293" s="30"/>
+      <c r="J293" s="28"/>
     </row>
     <row r="294" spans="10:10" ht="12.5">
-      <c r="J294" s="30"/>
+      <c r="J294" s="28"/>
     </row>
     <row r="295" spans="10:10" ht="12.5">
-      <c r="J295" s="30"/>
+      <c r="J295" s="28"/>
     </row>
     <row r="296" spans="10:10" ht="12.5">
-      <c r="J296" s="30"/>
+      <c r="J296" s="28"/>
     </row>
     <row r="297" spans="10:10" ht="12.5">
-      <c r="J297" s="30"/>
+      <c r="J297" s="28"/>
     </row>
     <row r="298" spans="10:10" ht="12.5">
-      <c r="J298" s="30"/>
+      <c r="J298" s="28"/>
     </row>
     <row r="299" spans="10:10" ht="12.5">
-      <c r="J299" s="30"/>
+      <c r="J299" s="28"/>
     </row>
     <row r="300" spans="10:10" ht="12.5">
-      <c r="J300" s="30"/>
+      <c r="J300" s="28"/>
     </row>
     <row r="301" spans="10:10" ht="12.5">
-      <c r="J301" s="30"/>
+      <c r="J301" s="28"/>
     </row>
     <row r="302" spans="10:10" ht="12.5">
-      <c r="J302" s="30"/>
+      <c r="J302" s="28"/>
     </row>
     <row r="303" spans="10:10" ht="12.5">
-      <c r="J303" s="30"/>
+      <c r="J303" s="28"/>
     </row>
     <row r="304" spans="10:10" ht="12.5">
-      <c r="J304" s="30"/>
+      <c r="J304" s="28"/>
     </row>
     <row r="305" spans="10:10" ht="12.5">
-      <c r="J305" s="30"/>
+      <c r="J305" s="28"/>
     </row>
     <row r="306" spans="10:10" ht="12.5">
-      <c r="J306" s="30"/>
+      <c r="J306" s="28"/>
     </row>
     <row r="307" spans="10:10" ht="12.5">
-      <c r="J307" s="30"/>
+      <c r="J307" s="28"/>
     </row>
     <row r="308" spans="10:10" ht="12.5">
-      <c r="J308" s="30"/>
+      <c r="J308" s="28"/>
     </row>
     <row r="309" spans="10:10" ht="12.5">
-      <c r="J309" s="30"/>
+      <c r="J309" s="28"/>
     </row>
     <row r="310" spans="10:10" ht="12.5">
-      <c r="J310" s="30"/>
+      <c r="J310" s="28"/>
     </row>
     <row r="311" spans="10:10" ht="12.5">
-      <c r="J311" s="30"/>
+      <c r="J311" s="28"/>
     </row>
     <row r="312" spans="10:10" ht="12.5">
-      <c r="J312" s="30"/>
+      <c r="J312" s="28"/>
     </row>
     <row r="313" spans="10:10" ht="12.5">
-      <c r="J313" s="30"/>
+      <c r="J313" s="28"/>
     </row>
     <row r="314" spans="10:10" ht="12.5">
-      <c r="J314" s="30"/>
+      <c r="J314" s="28"/>
     </row>
     <row r="315" spans="10:10" ht="12.5">
-      <c r="J315" s="30"/>
+      <c r="J315" s="28"/>
     </row>
     <row r="316" spans="10:10" ht="12.5">
-      <c r="J316" s="30"/>
+      <c r="J316" s="28"/>
     </row>
     <row r="317" spans="10:10" ht="12.5">
-      <c r="J317" s="30"/>
+      <c r="J317" s="28"/>
     </row>
     <row r="318" spans="10:10" ht="12.5">
-      <c r="J318" s="30"/>
+      <c r="J318" s="28"/>
     </row>
     <row r="319" spans="10:10" ht="12.5">
-      <c r="J319" s="30"/>
+      <c r="J319" s="28"/>
     </row>
     <row r="320" spans="10:10" ht="12.5">
-      <c r="J320" s="30"/>
+      <c r="J320" s="28"/>
     </row>
     <row r="321" spans="10:10" ht="12.5">
-      <c r="J321" s="30"/>
+      <c r="J321" s="28"/>
     </row>
     <row r="322" spans="10:10" ht="12.5">
-      <c r="J322" s="30"/>
+      <c r="J322" s="28"/>
     </row>
     <row r="323" spans="10:10" ht="12.5">
-      <c r="J323" s="30"/>
+      <c r="J323" s="28"/>
     </row>
     <row r="324" spans="10:10" ht="12.5">
-      <c r="J324" s="30"/>
+      <c r="J324" s="28"/>
     </row>
     <row r="325" spans="10:10" ht="12.5">
-      <c r="J325" s="30"/>
+      <c r="J325" s="28"/>
     </row>
     <row r="326" spans="10:10" ht="12.5">
-      <c r="J326" s="30"/>
+      <c r="J326" s="28"/>
     </row>
     <row r="327" spans="10:10" ht="12.5">
-      <c r="J327" s="30"/>
+      <c r="J327" s="28"/>
     </row>
     <row r="328" spans="10:10" ht="12.5">
-      <c r="J328" s="30"/>
+      <c r="J328" s="28"/>
     </row>
     <row r="329" spans="10:10" ht="12.5">
-      <c r="J329" s="30"/>
+      <c r="J329" s="28"/>
     </row>
     <row r="330" spans="10:10" ht="12.5">
-      <c r="J330" s="30"/>
+      <c r="J330" s="28"/>
     </row>
     <row r="331" spans="10:10" ht="12.5">
-      <c r="J331" s="30"/>
+      <c r="J331" s="28"/>
     </row>
     <row r="332" spans="10:10" ht="12.5">
-      <c r="J332" s="30"/>
+      <c r="J332" s="28"/>
     </row>
     <row r="333" spans="10:10" ht="12.5">
-      <c r="J333" s="30"/>
+      <c r="J333" s="28"/>
     </row>
     <row r="334" spans="10:10" ht="12.5">
-      <c r="J334" s="30"/>
+      <c r="J334" s="28"/>
     </row>
     <row r="335" spans="10:10" ht="12.5">
-      <c r="J335" s="30"/>
+      <c r="J335" s="28"/>
     </row>
     <row r="336" spans="10:10" ht="12.5">
-      <c r="J336" s="30"/>
+      <c r="J336" s="28"/>
     </row>
     <row r="337" spans="10:10" ht="12.5">
-      <c r="J337" s="30"/>
+      <c r="J337" s="28"/>
     </row>
     <row r="338" spans="10:10" ht="12.5">
-      <c r="J338" s="30"/>
+      <c r="J338" s="28"/>
     </row>
     <row r="339" spans="10:10" ht="12.5">
-      <c r="J339" s="30"/>
+      <c r="J339" s="28"/>
     </row>
     <row r="340" spans="10:10" ht="12.5">
-      <c r="J340" s="30"/>
+      <c r="J340" s="28"/>
     </row>
     <row r="341" spans="10:10" ht="12.5">
-      <c r="J341" s="30"/>
+      <c r="J341" s="28"/>
     </row>
     <row r="342" spans="10:10" ht="12.5">
-      <c r="J342" s="30"/>
+      <c r="J342" s="28"/>
     </row>
     <row r="343" spans="10:10" ht="12.5">
-      <c r="J343" s="30"/>
+      <c r="J343" s="28"/>
     </row>
     <row r="344" spans="10:10" ht="12.5">
-      <c r="J344" s="30"/>
+      <c r="J344" s="28"/>
     </row>
     <row r="345" spans="10:10" ht="12.5">
-      <c r="J345" s="30"/>
+      <c r="J345" s="28"/>
     </row>
     <row r="346" spans="10:10" ht="12.5">
-      <c r="J346" s="30"/>
+      <c r="J346" s="28"/>
     </row>
     <row r="347" spans="10:10" ht="12.5">
-      <c r="J347" s="30"/>
+      <c r="J347" s="28"/>
     </row>
     <row r="348" spans="10:10" ht="12.5">
-      <c r="J348" s="30"/>
+      <c r="J348" s="28"/>
     </row>
     <row r="349" spans="10:10" ht="12.5">
-      <c r="J349" s="30"/>
+      <c r="J349" s="28"/>
     </row>
     <row r="350" spans="10:10" ht="12.5">
-      <c r="J350" s="30"/>
+      <c r="J350" s="28"/>
     </row>
     <row r="351" spans="10:10" ht="12.5">
-      <c r="J351" s="30"/>
+      <c r="J351" s="28"/>
     </row>
     <row r="352" spans="10:10" ht="12.5">
-      <c r="J352" s="30"/>
+      <c r="J352" s="28"/>
     </row>
     <row r="353" spans="10:10" ht="12.5">
-      <c r="J353" s="30"/>
+      <c r="J353" s="28"/>
     </row>
     <row r="354" spans="10:10" ht="12.5">
-      <c r="J354" s="30"/>
+      <c r="J354" s="28"/>
     </row>
     <row r="355" spans="10:10" ht="12.5">
-      <c r="J355" s="30"/>
+      <c r="J355" s="28"/>
     </row>
     <row r="356" spans="10:10" ht="12.5">
-      <c r="J356" s="30"/>
+      <c r="J356" s="28"/>
     </row>
     <row r="357" spans="10:10" ht="12.5">
-      <c r="J357" s="30"/>
+      <c r="J357" s="28"/>
     </row>
     <row r="358" spans="10:10" ht="12.5">
-      <c r="J358" s="30"/>
+      <c r="J358" s="28"/>
     </row>
     <row r="359" spans="10:10" ht="12.5">
-      <c r="J359" s="30"/>
+      <c r="J359" s="28"/>
     </row>
     <row r="360" spans="10:10" ht="12.5">
-      <c r="J360" s="30"/>
+      <c r="J360" s="28"/>
     </row>
     <row r="361" spans="10:10" ht="12.5">
-      <c r="J361" s="30"/>
+      <c r="J361" s="28"/>
     </row>
     <row r="362" spans="10:10" ht="12.5">
-      <c r="J362" s="30"/>
+      <c r="J362" s="28"/>
     </row>
     <row r="363" spans="10:10" ht="12.5">
-      <c r="J363" s="30"/>
+      <c r="J363" s="28"/>
     </row>
     <row r="364" spans="10:10" ht="12.5">
-      <c r="J364" s="30"/>
+      <c r="J364" s="28"/>
     </row>
     <row r="365" spans="10:10" ht="12.5">
-      <c r="J365" s="30"/>
+      <c r="J365" s="28"/>
     </row>
     <row r="366" spans="10:10" ht="12.5">
-      <c r="J366" s="30"/>
+      <c r="J366" s="28"/>
     </row>
     <row r="367" spans="10:10" ht="12.5">
-      <c r="J367" s="30"/>
+      <c r="J367" s="28"/>
     </row>
     <row r="368" spans="10:10" ht="12.5">
-      <c r="J368" s="30"/>
+      <c r="J368" s="28"/>
     </row>
     <row r="369" spans="10:10" ht="12.5">
-      <c r="J369" s="30"/>
+      <c r="J369" s="28"/>
     </row>
     <row r="370" spans="10:10" ht="12.5">
-      <c r="J370" s="30"/>
+      <c r="J370" s="28"/>
     </row>
     <row r="371" spans="10:10" ht="12.5">
-      <c r="J371" s="30"/>
+      <c r="J371" s="28"/>
     </row>
     <row r="372" spans="10:10" ht="12.5">
-      <c r="J372" s="30"/>
+      <c r="J372" s="28"/>
     </row>
     <row r="373" spans="10:10" ht="12.5">
-      <c r="J373" s="30"/>
+      <c r="J373" s="28"/>
     </row>
     <row r="374" spans="10:10" ht="12.5">
-      <c r="J374" s="30"/>
+      <c r="J374" s="28"/>
     </row>
     <row r="375" spans="10:10" ht="12.5">
-      <c r="J375" s="30"/>
+      <c r="J375" s="28"/>
     </row>
     <row r="376" spans="10:10" ht="12.5">
-      <c r="J376" s="30"/>
+      <c r="J376" s="28"/>
     </row>
     <row r="377" spans="10:10" ht="12.5">
-      <c r="J377" s="30"/>
+      <c r="J377" s="28"/>
     </row>
     <row r="378" spans="10:10" ht="12.5">
-      <c r="J378" s="30"/>
+      <c r="J378" s="28"/>
     </row>
     <row r="379" spans="10:10" ht="12.5">
-      <c r="J379" s="30"/>
+      <c r="J379" s="28"/>
     </row>
     <row r="380" spans="10:10" ht="12.5">
-      <c r="J380" s="30"/>
+      <c r="J380" s="28"/>
     </row>
     <row r="381" spans="10:10" ht="12.5">
-      <c r="J381" s="30"/>
+      <c r="J381" s="28"/>
     </row>
     <row r="382" spans="10:10" ht="12.5">
-      <c r="J382" s="30"/>
+      <c r="J382" s="28"/>
     </row>
     <row r="383" spans="10:10" ht="12.5">
-      <c r="J383" s="30"/>
+      <c r="J383" s="28"/>
     </row>
     <row r="384" spans="10:10" ht="12.5">
-      <c r="J384" s="30"/>
+      <c r="J384" s="28"/>
     </row>
     <row r="385" spans="10:10" ht="12.5">
-      <c r="J385" s="30"/>
+      <c r="J385" s="28"/>
     </row>
     <row r="386" spans="10:10" ht="12.5">
-      <c r="J386" s="30"/>
+      <c r="J386" s="28"/>
     </row>
     <row r="387" spans="10:10" ht="12.5">
-      <c r="J387" s="30"/>
+      <c r="J387" s="28"/>
     </row>
     <row r="388" spans="10:10" ht="12.5">
-      <c r="J388" s="30"/>
+      <c r="J388" s="28"/>
     </row>
     <row r="389" spans="10:10" ht="12.5">
-      <c r="J389" s="30"/>
+      <c r="J389" s="28"/>
     </row>
     <row r="390" spans="10:10" ht="12.5">
-      <c r="J390" s="30"/>
+      <c r="J390" s="28"/>
     </row>
     <row r="391" spans="10:10" ht="12.5">
-      <c r="J391" s="30"/>
+      <c r="J391" s="28"/>
     </row>
     <row r="392" spans="10:10" ht="12.5">
-      <c r="J392" s="30"/>
+      <c r="J392" s="28"/>
     </row>
     <row r="393" spans="10:10" ht="12.5">
-      <c r="J393" s="30"/>
+      <c r="J393" s="28"/>
     </row>
     <row r="394" spans="10:10" ht="12.5">
-      <c r="J394" s="30"/>
+      <c r="J394" s="28"/>
     </row>
     <row r="395" spans="10:10" ht="12.5">
-      <c r="J395" s="30"/>
+      <c r="J395" s="28"/>
     </row>
     <row r="396" spans="10:10" ht="12.5">
-      <c r="J396" s="30"/>
+      <c r="J396" s="28"/>
     </row>
     <row r="397" spans="10:10" ht="12.5">
-      <c r="J397" s="30"/>
+      <c r="J397" s="28"/>
     </row>
     <row r="398" spans="10:10" ht="12.5">
-      <c r="J398" s="30"/>
+      <c r="J398" s="28"/>
     </row>
     <row r="399" spans="10:10" ht="12.5">
-      <c r="J399" s="30"/>
+      <c r="J399" s="28"/>
     </row>
     <row r="400" spans="10:10" ht="12.5">
-      <c r="J400" s="30"/>
+      <c r="J400" s="28"/>
     </row>
     <row r="401" spans="10:10" ht="12.5">
-      <c r="J401" s="30"/>
+      <c r="J401" s="28"/>
     </row>
     <row r="402" spans="10:10" ht="12.5">
-      <c r="J402" s="30"/>
+      <c r="J402" s="28"/>
     </row>
     <row r="403" spans="10:10" ht="12.5">
-      <c r="J403" s="30"/>
+      <c r="J403" s="28"/>
     </row>
     <row r="404" spans="10:10" ht="12.5">
-      <c r="J404" s="30"/>
+      <c r="J404" s="28"/>
     </row>
     <row r="405" spans="10:10" ht="12.5">
-      <c r="J405" s="30"/>
+      <c r="J405" s="28"/>
     </row>
     <row r="406" spans="10:10" ht="12.5">
-      <c r="J406" s="30"/>
+      <c r="J406" s="28"/>
     </row>
     <row r="407" spans="10:10" ht="12.5">
-      <c r="J407" s="30"/>
+      <c r="J407" s="28"/>
     </row>
     <row r="408" spans="10:10" ht="12.5">
-      <c r="J408" s="30"/>
+      <c r="J408" s="28"/>
     </row>
     <row r="409" spans="10:10" ht="12.5">
-      <c r="J409" s="30"/>
+      <c r="J409" s="28"/>
     </row>
     <row r="410" spans="10:10" ht="12.5">
-      <c r="J410" s="30"/>
+      <c r="J410" s="28"/>
     </row>
     <row r="411" spans="10:10" ht="12.5">
-      <c r="J411" s="30"/>
+      <c r="J411" s="28"/>
     </row>
     <row r="412" spans="10:10" ht="12.5">
-      <c r="J412" s="30"/>
+      <c r="J412" s="28"/>
     </row>
     <row r="413" spans="10:10" ht="12.5">
-      <c r="J413" s="30"/>
+      <c r="J413" s="28"/>
     </row>
     <row r="414" spans="10:10" ht="12.5">
-      <c r="J414" s="30"/>
+      <c r="J414" s="28"/>
     </row>
     <row r="415" spans="10:10" ht="12.5">
-      <c r="J415" s="30"/>
+      <c r="J415" s="28"/>
     </row>
     <row r="416" spans="10:10" ht="12.5">
-      <c r="J416" s="30"/>
+      <c r="J416" s="28"/>
     </row>
     <row r="417" spans="10:10" ht="12.5">
-      <c r="J417" s="30"/>
+      <c r="J417" s="28"/>
     </row>
     <row r="418" spans="10:10" ht="12.5">
-      <c r="J418" s="30"/>
+      <c r="J418" s="28"/>
     </row>
     <row r="419" spans="10:10" ht="12.5">
-      <c r="J419" s="30"/>
+      <c r="J419" s="28"/>
     </row>
     <row r="420" spans="10:10" ht="12.5">
-      <c r="J420" s="30"/>
+      <c r="J420" s="28"/>
     </row>
     <row r="421" spans="10:10" ht="12.5">
-      <c r="J421" s="30"/>
+      <c r="J421" s="28"/>
     </row>
     <row r="422" spans="10:10" ht="12.5">
-      <c r="J422" s="30"/>
+      <c r="J422" s="28"/>
     </row>
     <row r="423" spans="10:10" ht="12.5">
-      <c r="J423" s="30"/>
+      <c r="J423" s="28"/>
     </row>
     <row r="424" spans="10:10" ht="12.5">
-      <c r="J424" s="30"/>
+      <c r="J424" s="28"/>
     </row>
     <row r="425" spans="10:10" ht="12.5">
-      <c r="J425" s="30"/>
+      <c r="J425" s="28"/>
     </row>
     <row r="426" spans="10:10" ht="12.5">
-      <c r="J426" s="30"/>
+      <c r="J426" s="28"/>
     </row>
     <row r="427" spans="10:10" ht="12.5">
-      <c r="J427" s="30"/>
+      <c r="J427" s="28"/>
     </row>
     <row r="428" spans="10:10" ht="12.5">
-      <c r="J428" s="30"/>
+      <c r="J428" s="28"/>
     </row>
     <row r="429" spans="10:10" ht="12.5">
-      <c r="J429" s="30"/>
+      <c r="J429" s="28"/>
     </row>
     <row r="430" spans="10:10" ht="12.5">
-      <c r="J430" s="30"/>
+      <c r="J430" s="28"/>
     </row>
     <row r="431" spans="10:10" ht="12.5">
-      <c r="J431" s="30"/>
+      <c r="J431" s="28"/>
     </row>
     <row r="432" spans="10:10" ht="12.5">
-      <c r="J432" s="30"/>
+      <c r="J432" s="28"/>
     </row>
     <row r="433" spans="10:10" ht="12.5">
-      <c r="J433" s="30"/>
+      <c r="J433" s="28"/>
     </row>
     <row r="434" spans="10:10" ht="12.5">
-      <c r="J434" s="30"/>
+      <c r="J434" s="28"/>
     </row>
     <row r="435" spans="10:10" ht="12.5">
-      <c r="J435" s="30"/>
+      <c r="J435" s="28"/>
     </row>
     <row r="436" spans="10:10" ht="12.5">
-      <c r="J436" s="30"/>
+      <c r="J436" s="28"/>
     </row>
     <row r="437" spans="10:10" ht="12.5">
-      <c r="J437" s="30"/>
+      <c r="J437" s="28"/>
     </row>
     <row r="438" spans="10:10" ht="12.5">
-      <c r="J438" s="30"/>
+      <c r="J438" s="28"/>
     </row>
     <row r="439" spans="10:10" ht="12.5">
-      <c r="J439" s="30"/>
+      <c r="J439" s="28"/>
     </row>
     <row r="440" spans="10:10" ht="12.5">
-      <c r="J440" s="30"/>
+      <c r="J440" s="28"/>
     </row>
     <row r="441" spans="10:10" ht="12.5">
-      <c r="J441" s="30"/>
+      <c r="J441" s="28"/>
     </row>
     <row r="442" spans="10:10" ht="12.5">
-      <c r="J442" s="30"/>
+      <c r="J442" s="28"/>
     </row>
     <row r="443" spans="10:10" ht="12.5">
-      <c r="J443" s="30"/>
+      <c r="J443" s="28"/>
     </row>
     <row r="444" spans="10:10" ht="12.5">
-      <c r="J444" s="30"/>
+      <c r="J444" s="28"/>
     </row>
     <row r="445" spans="10:10" ht="12.5">
-      <c r="J445" s="30"/>
+      <c r="J445" s="28"/>
     </row>
     <row r="446" spans="10:10" ht="12.5">
-      <c r="J446" s="30"/>
+      <c r="J446" s="28"/>
     </row>
     <row r="447" spans="10:10" ht="12.5">
-      <c r="J447" s="30"/>
+      <c r="J447" s="28"/>
     </row>
     <row r="448" spans="10:10" ht="12.5">
-      <c r="J448" s="30"/>
+      <c r="J448" s="28"/>
     </row>
     <row r="449" spans="10:10" ht="12.5">
-      <c r="J449" s="30"/>
+      <c r="J449" s="28"/>
     </row>
     <row r="450" spans="10:10" ht="12.5">
-      <c r="J450" s="30"/>
+      <c r="J450" s="28"/>
     </row>
     <row r="451" spans="10:10" ht="12.5">
-      <c r="J451" s="30"/>
+      <c r="J451" s="28"/>
     </row>
     <row r="452" spans="10:10" ht="12.5">
-      <c r="J452" s="30"/>
+      <c r="J452" s="28"/>
     </row>
     <row r="453" spans="10:10" ht="12.5">
-      <c r="J453" s="30"/>
+      <c r="J453" s="28"/>
     </row>
     <row r="454" spans="10:10" ht="12.5">
-      <c r="J454" s="30"/>
+      <c r="J454" s="28"/>
     </row>
     <row r="455" spans="10:10" ht="12.5">
-      <c r="J455" s="30"/>
+      <c r="J455" s="28"/>
     </row>
     <row r="456" spans="10:10" ht="12.5">
-      <c r="J456" s="30"/>
+      <c r="J456" s="28"/>
     </row>
     <row r="457" spans="10:10" ht="12.5">
-      <c r="J457" s="30"/>
+      <c r="J457" s="28"/>
     </row>
     <row r="458" spans="10:10" ht="12.5">
-      <c r="J458" s="30"/>
+      <c r="J458" s="28"/>
     </row>
     <row r="459" spans="10:10" ht="12.5">
-      <c r="J459" s="30"/>
+      <c r="J459" s="28"/>
     </row>
     <row r="460" spans="10:10" ht="12.5">
-      <c r="J460" s="30"/>
+      <c r="J460" s="28"/>
     </row>
     <row r="461" spans="10:10" ht="12.5">
-      <c r="J461" s="30"/>
+      <c r="J461" s="28"/>
     </row>
     <row r="462" spans="10:10" ht="12.5">
-      <c r="J462" s="30"/>
+      <c r="J462" s="28"/>
     </row>
     <row r="463" spans="10:10" ht="12.5">
-      <c r="J463" s="30"/>
+      <c r="J463" s="28"/>
     </row>
     <row r="464" spans="10:10" ht="12.5">
-      <c r="J464" s="30"/>
+      <c r="J464" s="28"/>
     </row>
     <row r="465" spans="10:10" ht="12.5">
-      <c r="J465" s="30"/>
+      <c r="J465" s="28"/>
     </row>
     <row r="466" spans="10:10" ht="12.5">
-      <c r="J466" s="30"/>
+      <c r="J466" s="28"/>
     </row>
     <row r="467" spans="10:10" ht="12.5">
-      <c r="J467" s="30"/>
+      <c r="J467" s="28"/>
     </row>
     <row r="468" spans="10:10" ht="12.5">
-      <c r="J468" s="30"/>
+      <c r="J468" s="28"/>
     </row>
     <row r="469" spans="10:10" ht="12.5">
-      <c r="J469" s="30"/>
+      <c r="J469" s="28"/>
     </row>
     <row r="470" spans="10:10" ht="12.5">
-      <c r="J470" s="30"/>
+      <c r="J470" s="28"/>
     </row>
     <row r="471" spans="10:10" ht="12.5">
-      <c r="J471" s="30"/>
+      <c r="J471" s="28"/>
     </row>
     <row r="472" spans="10:10" ht="12.5">
-      <c r="J472" s="30"/>
+      <c r="J472" s="28"/>
     </row>
     <row r="473" spans="10:10" ht="12.5">
-      <c r="J473" s="30"/>
+      <c r="J473" s="28"/>
     </row>
     <row r="474" spans="10:10" ht="12.5">
-      <c r="J474" s="30"/>
+      <c r="J474" s="28"/>
     </row>
     <row r="475" spans="10:10" ht="12.5">
-      <c r="J475" s="30"/>
+      <c r="J475" s="28"/>
     </row>
     <row r="476" spans="10:10" ht="12.5">
-      <c r="J476" s="30"/>
+      <c r="J476" s="28"/>
     </row>
     <row r="477" spans="10:10" ht="12.5">
-      <c r="J477" s="30"/>
+      <c r="J477" s="28"/>
     </row>
     <row r="478" spans="10:10" ht="12.5">
-      <c r="J478" s="30"/>
+      <c r="J478" s="28"/>
     </row>
     <row r="479" spans="10:10" ht="12.5">
-      <c r="J479" s="30"/>
+      <c r="J479" s="28"/>
     </row>
     <row r="480" spans="10:10" ht="12.5">
-      <c r="J480" s="30"/>
+      <c r="J480" s="28"/>
     </row>
     <row r="481" spans="10:10" ht="12.5">
-      <c r="J481" s="30"/>
+      <c r="J481" s="28"/>
     </row>
     <row r="482" spans="10:10" ht="12.5">
-      <c r="J482" s="30"/>
+      <c r="J482" s="28"/>
     </row>
     <row r="483" spans="10:10" ht="12.5">
-      <c r="J483" s="30"/>
+      <c r="J483" s="28"/>
     </row>
     <row r="484" spans="10:10" ht="12.5">
-      <c r="J484" s="30"/>
+      <c r="J484" s="28"/>
     </row>
     <row r="485" spans="10:10" ht="12.5">
-      <c r="J485" s="30"/>
+      <c r="J485" s="28"/>
     </row>
     <row r="486" spans="10:10" ht="12.5">
-      <c r="J486" s="30"/>
+      <c r="J486" s="28"/>
     </row>
     <row r="487" spans="10:10" ht="12.5">
-      <c r="J487" s="30"/>
+      <c r="J487" s="28"/>
     </row>
     <row r="488" spans="10:10" ht="12.5">
-      <c r="J488" s="30"/>
+      <c r="J488" s="28"/>
     </row>
     <row r="489" spans="10:10" ht="12.5">
-      <c r="J489" s="30"/>
+      <c r="J489" s="28"/>
     </row>
     <row r="490" spans="10:10" ht="12.5">
-      <c r="J490" s="30"/>
+      <c r="J490" s="28"/>
     </row>
     <row r="491" spans="10:10" ht="12.5">
-      <c r="J491" s="30"/>
+      <c r="J491" s="28"/>
     </row>
     <row r="492" spans="10:10" ht="12.5">
-      <c r="J492" s="30"/>
+      <c r="J492" s="28"/>
     </row>
     <row r="493" spans="10:10" ht="12.5">
-      <c r="J493" s="30"/>
+      <c r="J493" s="28"/>
     </row>
     <row r="494" spans="10:10" ht="12.5">
-      <c r="J494" s="30"/>
+      <c r="J494" s="28"/>
     </row>
     <row r="495" spans="10:10" ht="12.5">
-      <c r="J495" s="30"/>
+      <c r="J495" s="28"/>
     </row>
     <row r="496" spans="10:10" ht="12.5">
-      <c r="J496" s="30"/>
+      <c r="J496" s="28"/>
     </row>
     <row r="497" spans="10:10" ht="12.5">
-      <c r="J497" s="30"/>
+      <c r="J497" s="28"/>
     </row>
     <row r="498" spans="10:10" ht="12.5">
-      <c r="J498" s="30"/>
+      <c r="J498" s="28"/>
     </row>
     <row r="499" spans="10:10" ht="12.5">
-      <c r="J499" s="30"/>
+      <c r="J499" s="28"/>
     </row>
     <row r="500" spans="10:10" ht="12.5">
-      <c r="J500" s="30"/>
+      <c r="J500" s="28"/>
     </row>
     <row r="501" spans="10:10" ht="12.5">
-      <c r="J501" s="30"/>
+      <c r="J501" s="28"/>
     </row>
     <row r="502" spans="10:10" ht="12.5">
-      <c r="J502" s="30"/>
+      <c r="J502" s="28"/>
     </row>
     <row r="503" spans="10:10" ht="12.5">
-      <c r="J503" s="30"/>
+      <c r="J503" s="28"/>
     </row>
     <row r="504" spans="10:10" ht="12.5">
-      <c r="J504" s="30"/>
+      <c r="J504" s="28"/>
     </row>
     <row r="505" spans="10:10" ht="12.5">
-      <c r="J505" s="30"/>
+      <c r="J505" s="28"/>
     </row>
     <row r="506" spans="10:10" ht="12.5">
-      <c r="J506" s="30"/>
+      <c r="J506" s="28"/>
     </row>
     <row r="507" spans="10:10" ht="12.5">
-      <c r="J507" s="30"/>
+      <c r="J507" s="28"/>
     </row>
     <row r="508" spans="10:10" ht="12.5">
-      <c r="J508" s="30"/>
+      <c r="J508" s="28"/>
     </row>
     <row r="509" spans="10:10" ht="12.5">
-      <c r="J509" s="30"/>
+      <c r="J509" s="28"/>
     </row>
     <row r="510" spans="10:10" ht="12.5">
-      <c r="J510" s="30"/>
+      <c r="J510" s="28"/>
     </row>
     <row r="511" spans="10:10" ht="12.5">
-      <c r="J511" s="30"/>
+      <c r="J511" s="28"/>
     </row>
     <row r="512" spans="10:10" ht="12.5">
-      <c r="J512" s="30"/>
+      <c r="J512" s="28"/>
     </row>
     <row r="513" spans="10:10" ht="12.5">
-      <c r="J513" s="30"/>
+      <c r="J513" s="28"/>
     </row>
     <row r="514" spans="10:10" ht="12.5">
-      <c r="J514" s="30"/>
+      <c r="J514" s="28"/>
     </row>
     <row r="515" spans="10:10" ht="12.5">
-      <c r="J515" s="30"/>
+      <c r="J515" s="28"/>
     </row>
     <row r="516" spans="10:10" ht="12.5">
-      <c r="J516" s="30"/>
+      <c r="J516" s="28"/>
     </row>
     <row r="517" spans="10:10" ht="12.5">
-      <c r="J517" s="30"/>
+      <c r="J517" s="28"/>
     </row>
     <row r="518" spans="10:10" ht="12.5">
-      <c r="J518" s="30"/>
+      <c r="J518" s="28"/>
     </row>
     <row r="519" spans="10:10" ht="12.5">
-      <c r="J519" s="30"/>
+      <c r="J519" s="28"/>
     </row>
     <row r="520" spans="10:10" ht="12.5">
-      <c r="J520" s="30"/>
+      <c r="J520" s="28"/>
     </row>
     <row r="521" spans="10:10" ht="12.5">
-      <c r="J521" s="30"/>
+      <c r="J521" s="28"/>
     </row>
     <row r="522" spans="10:10" ht="12.5">
-      <c r="J522" s="30"/>
+      <c r="J522" s="28"/>
     </row>
     <row r="523" spans="10:10" ht="12.5">
-      <c r="J523" s="30"/>
+      <c r="J523" s="28"/>
     </row>
     <row r="524" spans="10:10" ht="12.5">
-      <c r="J524" s="30"/>
+      <c r="J524" s="28"/>
     </row>
     <row r="525" spans="10:10" ht="12.5">
-      <c r="J525" s="30"/>
+      <c r="J525" s="28"/>
     </row>
     <row r="526" spans="10:10" ht="12.5">
-      <c r="J526" s="30"/>
+      <c r="J526" s="28"/>
     </row>
     <row r="527" spans="10:10" ht="12.5">
-      <c r="J527" s="30"/>
+      <c r="J527" s="28"/>
     </row>
     <row r="528" spans="10:10" ht="12.5">
-      <c r="J528" s="30"/>
+      <c r="J528" s="28"/>
     </row>
     <row r="529" spans="10:10" ht="12.5">
-      <c r="J529" s="30"/>
+      <c r="J529" s="28"/>
     </row>
     <row r="530" spans="10:10" ht="12.5">
-      <c r="J530" s="30"/>
+      <c r="J530" s="28"/>
     </row>
     <row r="531" spans="10:10" ht="12.5">
-      <c r="J531" s="30"/>
+      <c r="J531" s="28"/>
     </row>
     <row r="532" spans="10:10" ht="12.5">
-      <c r="J532" s="30"/>
+      <c r="J532" s="28"/>
     </row>
     <row r="533" spans="10:10" ht="12.5">
-      <c r="J533" s="30"/>
+      <c r="J533" s="28"/>
     </row>
     <row r="534" spans="10:10" ht="12.5">
-      <c r="J534" s="30"/>
+      <c r="J534" s="28"/>
     </row>
     <row r="535" spans="10:10" ht="12.5">
-      <c r="J535" s="30"/>
+      <c r="J535" s="28"/>
     </row>
     <row r="536" spans="10:10" ht="12.5">
-      <c r="J536" s="30"/>
+      <c r="J536" s="28"/>
     </row>
     <row r="537" spans="10:10" ht="12.5">
-      <c r="J537" s="30"/>
+      <c r="J537" s="28"/>
     </row>
     <row r="538" spans="10:10" ht="12.5">
-      <c r="J538" s="30"/>
+      <c r="J538" s="28"/>
     </row>
     <row r="539" spans="10:10" ht="12.5">
-      <c r="J539" s="30"/>
+      <c r="J539" s="28"/>
     </row>
     <row r="540" spans="10:10" ht="12.5">
-      <c r="J540" s="30"/>
+      <c r="J540" s="28"/>
     </row>
     <row r="541" spans="10:10" ht="12.5">
-      <c r="J541" s="30"/>
+      <c r="J541" s="28"/>
     </row>
     <row r="542" spans="10:10" ht="12.5">
-      <c r="J542" s="30"/>
+      <c r="J542" s="28"/>
     </row>
     <row r="543" spans="10:10" ht="12.5">
-      <c r="J543" s="30"/>
+      <c r="J543" s="28"/>
     </row>
     <row r="544" spans="10:10" ht="12.5">
-      <c r="J544" s="30"/>
+      <c r="J544" s="28"/>
     </row>
     <row r="545" spans="10:10" ht="12.5">
-      <c r="J545" s="30"/>
+      <c r="J545" s="28"/>
     </row>
     <row r="546" spans="10:10" ht="12.5">
-      <c r="J546" s="30"/>
+      <c r="J546" s="28"/>
     </row>
     <row r="547" spans="10:10" ht="12.5">
-      <c r="J547" s="30"/>
+      <c r="J547" s="28"/>
     </row>
     <row r="548" spans="10:10" ht="12.5">
-      <c r="J548" s="30"/>
+      <c r="J548" s="28"/>
     </row>
     <row r="549" spans="10:10" ht="12.5">
-      <c r="J549" s="30"/>
+      <c r="J549" s="28"/>
     </row>
     <row r="550" spans="10:10" ht="12.5">
-      <c r="J550" s="30"/>
+      <c r="J550" s="28"/>
     </row>
     <row r="551" spans="10:10" ht="12.5">
-      <c r="J551" s="30"/>
+      <c r="J551" s="28"/>
     </row>
     <row r="552" spans="10:10" ht="12.5">
-      <c r="J552" s="30"/>
+      <c r="J552" s="28"/>
     </row>
     <row r="553" spans="10:10" ht="12.5">
-      <c r="J553" s="30"/>
+      <c r="J553" s="28"/>
     </row>
     <row r="554" spans="10:10" ht="12.5">
-      <c r="J554" s="30"/>
+      <c r="J554" s="28"/>
     </row>
     <row r="555" spans="10:10" ht="12.5">
-      <c r="J555" s="30"/>
+      <c r="J555" s="28"/>
     </row>
     <row r="556" spans="10:10" ht="12.5">
-      <c r="J556" s="30"/>
+      <c r="J556" s="28"/>
     </row>
     <row r="557" spans="10:10" ht="12.5">
-      <c r="J557" s="30"/>
+      <c r="J557" s="28"/>
     </row>
     <row r="558" spans="10:10" ht="12.5">
-      <c r="J558" s="30"/>
+      <c r="J558" s="28"/>
     </row>
     <row r="559" spans="10:10" ht="12.5">
-      <c r="J559" s="30"/>
+      <c r="J559" s="28"/>
     </row>
     <row r="560" spans="10:10" ht="12.5">
-      <c r="J560" s="30"/>
+      <c r="J560" s="28"/>
     </row>
     <row r="561" spans="10:10" ht="12.5">
-      <c r="J561" s="30"/>
+      <c r="J561" s="28"/>
     </row>
     <row r="562" spans="10:10" ht="12.5">
-      <c r="J562" s="30"/>
+      <c r="J562" s="28"/>
     </row>
     <row r="563" spans="10:10" ht="12.5">
-      <c r="J563" s="30"/>
+      <c r="J563" s="28"/>
     </row>
     <row r="564" spans="10:10" ht="12.5">
-      <c r="J564" s="30"/>
+      <c r="J564" s="28"/>
     </row>
     <row r="565" spans="10:10" ht="12.5">
-      <c r="J565" s="30"/>
+      <c r="J565" s="28"/>
     </row>
     <row r="566" spans="10:10" ht="12.5">
-      <c r="J566" s="30"/>
+      <c r="J566" s="28"/>
     </row>
     <row r="567" spans="10:10" ht="12.5">
-      <c r="J567" s="30"/>
+      <c r="J567" s="28"/>
     </row>
     <row r="568" spans="10:10" ht="12.5">
-      <c r="J568" s="30"/>
+      <c r="J568" s="28"/>
     </row>
     <row r="569" spans="10:10" ht="12.5">
-      <c r="J569" s="30"/>
+      <c r="J569" s="28"/>
     </row>
     <row r="570" spans="10:10" ht="12.5">
-      <c r="J570" s="30"/>
+      <c r="J570" s="28"/>
     </row>
     <row r="571" spans="10:10" ht="12.5">
-      <c r="J571" s="30"/>
+      <c r="J571" s="28"/>
     </row>
     <row r="572" spans="10:10" ht="12.5">
-      <c r="J572" s="30"/>
+      <c r="J572" s="28"/>
     </row>
     <row r="573" spans="10:10" ht="12.5">
-      <c r="J573" s="30"/>
+      <c r="J573" s="28"/>
     </row>
     <row r="574" spans="10:10" ht="12.5">
-      <c r="J574" s="30"/>
+      <c r="J574" s="28"/>
     </row>
     <row r="575" spans="10:10" ht="12.5">
-      <c r="J575" s="30"/>
+      <c r="J575" s="28"/>
     </row>
     <row r="576" spans="10:10" ht="12.5">
-      <c r="J576" s="30"/>
+      <c r="J576" s="28"/>
     </row>
     <row r="577" spans="10:10" ht="12.5">
-      <c r="J577" s="30"/>
+      <c r="J577" s="28"/>
     </row>
     <row r="578" spans="10:10" ht="12.5">
-      <c r="J578" s="30"/>
+      <c r="J578" s="28"/>
     </row>
     <row r="579" spans="10:10" ht="12.5">
-      <c r="J579" s="30"/>
+      <c r="J579" s="28"/>
     </row>
     <row r="580" spans="10:10" ht="12.5">
-      <c r="J580" s="30"/>
+      <c r="J580" s="28"/>
     </row>
     <row r="581" spans="10:10" ht="12.5">
-      <c r="J581" s="30"/>
+      <c r="J581" s="28"/>
     </row>
     <row r="582" spans="10:10" ht="12.5">
-      <c r="J582" s="30"/>
+      <c r="J582" s="28"/>
     </row>
     <row r="583" spans="10:10" ht="12.5">
-      <c r="J583" s="30"/>
+      <c r="J583" s="28"/>
     </row>
     <row r="584" spans="10:10" ht="12.5">
-      <c r="J584" s="30"/>
+      <c r="J584" s="28"/>
     </row>
     <row r="585" spans="10:10" ht="12.5">
-      <c r="J585" s="30"/>
+      <c r="J585" s="28"/>
     </row>
     <row r="586" spans="10:10" ht="12.5">
-      <c r="J586" s="30"/>
+      <c r="J586" s="28"/>
     </row>
     <row r="587" spans="10:10" ht="12.5">
-      <c r="J587" s="30"/>
+      <c r="J587" s="28"/>
     </row>
     <row r="588" spans="10:10" ht="12.5">
-      <c r="J588" s="30"/>
+      <c r="J588" s="28"/>
     </row>
     <row r="589" spans="10:10" ht="12.5">
-      <c r="J589" s="30"/>
+      <c r="J589" s="28"/>
     </row>
     <row r="590" spans="10:10" ht="12.5">
-      <c r="J590" s="30"/>
+      <c r="J590" s="28"/>
     </row>
     <row r="591" spans="10:10" ht="12.5">
-      <c r="J591" s="30"/>
+      <c r="J591" s="28"/>
     </row>
     <row r="592" spans="10:10" ht="12.5">
-      <c r="J592" s="30"/>
+      <c r="J592" s="28"/>
     </row>
     <row r="593" spans="10:10" ht="12.5">
-      <c r="J593" s="30"/>
+      <c r="J593" s="28"/>
     </row>
     <row r="594" spans="10:10" ht="12.5">
-      <c r="J594" s="30"/>
+      <c r="J594" s="28"/>
     </row>
     <row r="595" spans="10:10" ht="12.5">
-      <c r="J595" s="30"/>
+      <c r="J595" s="28"/>
     </row>
     <row r="596" spans="10:10" ht="12.5">
-      <c r="J596" s="30"/>
+      <c r="J596" s="28"/>
     </row>
     <row r="597" spans="10:10" ht="12.5">
-      <c r="J597" s="30"/>
+      <c r="J597" s="28"/>
     </row>
     <row r="598" spans="10:10" ht="12.5">
-      <c r="J598" s="30"/>
+      <c r="J598" s="28"/>
     </row>
     <row r="599" spans="10:10" ht="12.5">
-      <c r="J599" s="30"/>
+      <c r="J599" s="28"/>
     </row>
     <row r="600" spans="10:10" ht="12.5">
-      <c r="J600" s="30"/>
+      <c r="J600" s="28"/>
     </row>
     <row r="601" spans="10:10" ht="12.5">
-      <c r="J601" s="30"/>
+      <c r="J601" s="28"/>
     </row>
     <row r="602" spans="10:10" ht="12.5">
-      <c r="J602" s="30"/>
+      <c r="J602" s="28"/>
     </row>
     <row r="603" spans="10:10" ht="12.5">
-      <c r="J603" s="30"/>
+      <c r="J603" s="28"/>
     </row>
     <row r="604" spans="10:10" ht="12.5">
-      <c r="J604" s="30"/>
+      <c r="J604" s="28"/>
     </row>
     <row r="605" spans="10:10" ht="12.5">
-      <c r="J605" s="30"/>
+      <c r="J605" s="28"/>
     </row>
     <row r="606" spans="10:10" ht="12.5">
-      <c r="J606" s="30"/>
+      <c r="J606" s="28"/>
     </row>
     <row r="607" spans="10:10" ht="12.5">
-      <c r="J607" s="30"/>
+      <c r="J607" s="28"/>
     </row>
     <row r="608" spans="10:10" ht="12.5">
-      <c r="J608" s="30"/>
+      <c r="J608" s="28"/>
     </row>
     <row r="609" spans="10:10" ht="12.5">
-      <c r="J609" s="30"/>
+      <c r="J609" s="28"/>
     </row>
     <row r="610" spans="10:10" ht="12.5">
-      <c r="J610" s="30"/>
+      <c r="J610" s="28"/>
     </row>
     <row r="611" spans="10:10" ht="12.5">
-      <c r="J611" s="30"/>
+      <c r="J611" s="28"/>
     </row>
     <row r="612" spans="10:10" ht="12.5">
-      <c r="J612" s="30"/>
+      <c r="J612" s="28"/>
     </row>
     <row r="613" spans="10:10" ht="12.5">
-      <c r="J613" s="30"/>
+      <c r="J613" s="28"/>
     </row>
     <row r="614" spans="10:10" ht="12.5">
-      <c r="J614" s="30"/>
+      <c r="J614" s="28"/>
     </row>
     <row r="615" spans="10:10" ht="12.5">
-      <c r="J615" s="30"/>
+      <c r="J615" s="28"/>
     </row>
     <row r="616" spans="10:10" ht="12.5">
-      <c r="J616" s="30"/>
+      <c r="J616" s="28"/>
     </row>
     <row r="617" spans="10:10" ht="12.5">
-      <c r="J617" s="30"/>
+      <c r="J617" s="28"/>
     </row>
     <row r="618" spans="10:10" ht="12.5">
-      <c r="J618" s="30"/>
+      <c r="J618" s="28"/>
     </row>
     <row r="619" spans="10:10" ht="12.5">
-      <c r="J619" s="30"/>
+      <c r="J619" s="28"/>
     </row>
     <row r="620" spans="10:10" ht="12.5">
-      <c r="J620" s="30"/>
+      <c r="J620" s="28"/>
     </row>
     <row r="621" spans="10:10" ht="12.5">
-      <c r="J621" s="30"/>
+      <c r="J621" s="28"/>
     </row>
     <row r="622" spans="10:10" ht="12.5">
-      <c r="J622" s="30"/>
+      <c r="J622" s="28"/>
     </row>
     <row r="623" spans="10:10" ht="12.5">
-      <c r="J623" s="30"/>
+      <c r="J623" s="28"/>
     </row>
     <row r="624" spans="10:10" ht="12.5">
-      <c r="J624" s="30"/>
+      <c r="J624" s="28"/>
     </row>
     <row r="625" spans="10:10" ht="12.5">
-      <c r="J625" s="30"/>
+      <c r="J625" s="28"/>
     </row>
     <row r="626" spans="10:10" ht="12.5">
-      <c r="J626" s="30"/>
+      <c r="J626" s="28"/>
     </row>
     <row r="627" spans="10:10" ht="12.5">
-      <c r="J627" s="30"/>
+      <c r="J627" s="28"/>
     </row>
     <row r="628" spans="10:10" ht="12.5">
-      <c r="J628" s="30"/>
+      <c r="J628" s="28"/>
     </row>
     <row r="629" spans="10:10" ht="12.5">
-      <c r="J629" s="30"/>
+      <c r="J629" s="28"/>
     </row>
     <row r="630" spans="10:10" ht="12.5">
-      <c r="J630" s="30"/>
+      <c r="J630" s="28"/>
     </row>
     <row r="631" spans="10:10" ht="12.5">
-      <c r="J631" s="30"/>
+      <c r="J631" s="28"/>
     </row>
     <row r="632" spans="10:10" ht="12.5">
-      <c r="J632" s="30"/>
+      <c r="J632" s="28"/>
     </row>
     <row r="633" spans="10:10" ht="12.5">
-      <c r="J633" s="30"/>
+      <c r="J633" s="28"/>
     </row>
     <row r="634" spans="10:10" ht="12.5">
-      <c r="J634" s="30"/>
+      <c r="J634" s="28"/>
     </row>
     <row r="635" spans="10:10" ht="12.5">
-      <c r="J635" s="30"/>
+      <c r="J635" s="28"/>
     </row>
     <row r="636" spans="10:10" ht="12.5">
-      <c r="J636" s="30"/>
+      <c r="J636" s="28"/>
     </row>
     <row r="637" spans="10:10" ht="12.5">
-      <c r="J637" s="30"/>
+      <c r="J637" s="28"/>
     </row>
     <row r="638" spans="10:10" ht="12.5">
-      <c r="J638" s="30"/>
+      <c r="J638" s="28"/>
     </row>
     <row r="639" spans="10:10" ht="12.5">
-      <c r="J639" s="30"/>
+      <c r="J639" s="28"/>
     </row>
     <row r="640" spans="10:10" ht="12.5">
-      <c r="J640" s="30"/>
+      <c r="J640" s="28"/>
     </row>
     <row r="641" spans="10:10" ht="12.5">
-      <c r="J641" s="30"/>
+      <c r="J641" s="28"/>
     </row>
     <row r="642" spans="10:10" ht="12.5">
-      <c r="J642" s="30"/>
+      <c r="J642" s="28"/>
     </row>
     <row r="643" spans="10:10" ht="12.5">
-      <c r="J643" s="30"/>
+      <c r="J643" s="28"/>
     </row>
     <row r="644" spans="10:10" ht="12.5">
-      <c r="J644" s="30"/>
+      <c r="J644" s="28"/>
     </row>
     <row r="645" spans="10:10" ht="12.5">
-      <c r="J645" s="30"/>
+      <c r="J645" s="28"/>
     </row>
     <row r="646" spans="10:10" ht="12.5">
-      <c r="J646" s="30"/>
+      <c r="J646" s="28"/>
     </row>
     <row r="647" spans="10:10" ht="12.5">
-      <c r="J647" s="30"/>
+      <c r="J647" s="28"/>
     </row>
     <row r="648" spans="10:10" ht="12.5">
-      <c r="J648" s="30"/>
+      <c r="J648" s="28"/>
     </row>
     <row r="649" spans="10:10" ht="12.5">
-      <c r="J649" s="30"/>
+      <c r="J649" s="28"/>
     </row>
     <row r="650" spans="10:10" ht="12.5">
-      <c r="J650" s="30"/>
+      <c r="J650" s="28"/>
     </row>
     <row r="651" spans="10:10" ht="12.5">
-      <c r="J651" s="30"/>
+      <c r="J651" s="28"/>
     </row>
     <row r="652" spans="10:10" ht="12.5">
-      <c r="J652" s="30"/>
+      <c r="J652" s="28"/>
     </row>
     <row r="653" spans="10:10" ht="12.5">
-      <c r="J653" s="30"/>
+      <c r="J653" s="28"/>
     </row>
     <row r="654" spans="10:10" ht="12.5">
-      <c r="J654" s="30"/>
+      <c r="J654" s="28"/>
     </row>
     <row r="655" spans="10:10" ht="12.5">
-      <c r="J655" s="30"/>
+      <c r="J655" s="28"/>
     </row>
     <row r="656" spans="10:10" ht="12.5">
-      <c r="J656" s="30"/>
+      <c r="J656" s="28"/>
     </row>
     <row r="657" spans="10:10" ht="12.5">
-      <c r="J657" s="30"/>
+      <c r="J657" s="28"/>
     </row>
     <row r="658" spans="10:10" ht="12.5">
-      <c r="J658" s="30"/>
+      <c r="J658" s="28"/>
     </row>
     <row r="659" spans="10:10" ht="12.5">
-      <c r="J659" s="30"/>
+      <c r="J659" s="28"/>
     </row>
     <row r="660" spans="10:10" ht="12.5">
-      <c r="J660" s="30"/>
+      <c r="J660" s="28"/>
     </row>
     <row r="661" spans="10:10" ht="12.5">
-      <c r="J661" s="30"/>
+      <c r="J661" s="28"/>
     </row>
     <row r="662" spans="10:10" ht="12.5">
-      <c r="J662" s="30"/>
+      <c r="J662" s="28"/>
     </row>
     <row r="663" spans="10:10" ht="12.5">
-      <c r="J663" s="30"/>
+      <c r="J663" s="28"/>
     </row>
     <row r="664" spans="10:10" ht="12.5">
-      <c r="J664" s="30"/>
+      <c r="J664" s="28"/>
     </row>
     <row r="665" spans="10:10" ht="12.5">
-      <c r="J665" s="30"/>
+      <c r="J665" s="28"/>
     </row>
     <row r="666" spans="10:10" ht="12.5">
-      <c r="J666" s="30"/>
+      <c r="J666" s="28"/>
     </row>
     <row r="667" spans="10:10" ht="12.5">
-      <c r="J667" s="30"/>
+      <c r="J667" s="28"/>
     </row>
     <row r="668" spans="10:10" ht="12.5">
-      <c r="J668" s="30"/>
+      <c r="J668" s="28"/>
     </row>
     <row r="669" spans="10:10" ht="12.5">
-      <c r="J669" s="30"/>
+      <c r="J669" s="28"/>
     </row>
     <row r="670" spans="10:10" ht="12.5">
-      <c r="J670" s="30"/>
+      <c r="J670" s="28"/>
     </row>
     <row r="671" spans="10:10" ht="12.5">
-      <c r="J671" s="30"/>
+      <c r="J671" s="28"/>
     </row>
     <row r="672" spans="10:10" ht="12.5">
-      <c r="J672" s="30"/>
+      <c r="J672" s="28"/>
     </row>
     <row r="673" spans="10:10" ht="12.5">
-      <c r="J673" s="30"/>
+      <c r="J673" s="28"/>
     </row>
     <row r="674" spans="10:10" ht="12.5">
-      <c r="J674" s="30"/>
+      <c r="J674" s="28"/>
     </row>
     <row r="675" spans="10:10" ht="12.5">
-      <c r="J675" s="30"/>
+      <c r="J675" s="28"/>
     </row>
     <row r="676" spans="10:10" ht="12.5">
-      <c r="J676" s="30"/>
+      <c r="J676" s="28"/>
     </row>
     <row r="677" spans="10:10" ht="12.5">
-      <c r="J677" s="30"/>
+      <c r="J677" s="28"/>
     </row>
     <row r="678" spans="10:10" ht="12.5">
-      <c r="J678" s="30"/>
+      <c r="J678" s="28"/>
     </row>
     <row r="679" spans="10:10" ht="12.5">
-      <c r="J679" s="30"/>
+      <c r="J679" s="28"/>
     </row>
     <row r="680" spans="10:10" ht="12.5">
-      <c r="J680" s="30"/>
+      <c r="J680" s="28"/>
     </row>
     <row r="681" spans="10:10" ht="12.5">
-      <c r="J681" s="30"/>
+      <c r="J681" s="28"/>
     </row>
     <row r="682" spans="10:10" ht="12.5">
-      <c r="J682" s="30"/>
+      <c r="J682" s="28"/>
     </row>
     <row r="683" spans="10:10" ht="12.5">
-      <c r="J683" s="30"/>
+      <c r="J683" s="28"/>
     </row>
     <row r="684" spans="10:10" ht="12.5">
-      <c r="J684" s="30"/>
+      <c r="J684" s="28"/>
     </row>
     <row r="685" spans="10:10" ht="12.5">
-      <c r="J685" s="30"/>
+      <c r="J685" s="28"/>
     </row>
     <row r="686" spans="10:10" ht="12.5">
-      <c r="J686" s="30"/>
+      <c r="J686" s="28"/>
     </row>
     <row r="687" spans="10:10" ht="12.5">
-      <c r="J687" s="30"/>
+      <c r="J687" s="28"/>
     </row>
     <row r="688" spans="10:10" ht="12.5">
-      <c r="J688" s="30"/>
+      <c r="J688" s="28"/>
     </row>
     <row r="689" spans="10:10" ht="12.5">
-      <c r="J689" s="30"/>
+      <c r="J689" s="28"/>
     </row>
     <row r="690" spans="10:10" ht="12.5">
-      <c r="J690" s="30"/>
+      <c r="J690" s="28"/>
     </row>
     <row r="691" spans="10:10" ht="12.5">
-      <c r="J691" s="30"/>
+      <c r="J691" s="28"/>
     </row>
     <row r="692" spans="10:10" ht="12.5">
-      <c r="J692" s="30"/>
+      <c r="J692" s="28"/>
     </row>
     <row r="693" spans="10:10" ht="12.5">
-      <c r="J693" s="30"/>
+      <c r="J693" s="28"/>
     </row>
     <row r="694" spans="10:10" ht="12.5">
-      <c r="J694" s="30"/>
+      <c r="J694" s="28"/>
     </row>
     <row r="695" spans="10:10" ht="12.5">
-      <c r="J695" s="30"/>
+      <c r="J695" s="28"/>
     </row>
     <row r="696" spans="10:10" ht="12.5">
-      <c r="J696" s="30"/>
+      <c r="J696" s="28"/>
     </row>
     <row r="697" spans="10:10" ht="12.5">
-      <c r="J697" s="30"/>
+      <c r="J697" s="28"/>
     </row>
     <row r="698" spans="10:10" ht="12.5">
-      <c r="J698" s="30"/>
+      <c r="J698" s="28"/>
     </row>
     <row r="699" spans="10:10" ht="12.5">
-      <c r="J699" s="30"/>
+      <c r="J699" s="28"/>
     </row>
     <row r="700" spans="10:10" ht="12.5">
-      <c r="J700" s="30"/>
+      <c r="J700" s="28"/>
     </row>
     <row r="701" spans="10:10" ht="12.5">
-      <c r="J701" s="30"/>
+      <c r="J701" s="28"/>
     </row>
     <row r="702" spans="10:10" ht="12.5">
-      <c r="J702" s="30"/>
+      <c r="J702" s="28"/>
     </row>
     <row r="703" spans="10:10" ht="12.5">
-      <c r="J703" s="30"/>
+      <c r="J703" s="28"/>
     </row>
     <row r="704" spans="10:10" ht="12.5">
-      <c r="J704" s="30"/>
+      <c r="J704" s="28"/>
     </row>
     <row r="705" spans="10:10" ht="12.5">
-      <c r="J705" s="30"/>
+      <c r="J705" s="28"/>
     </row>
     <row r="706" spans="10:10" ht="12.5">
-      <c r="J706" s="30"/>
+      <c r="J706" s="28"/>
     </row>
     <row r="707" spans="10:10" ht="12.5">
-      <c r="J707" s="30"/>
+      <c r="J707" s="28"/>
     </row>
     <row r="708" spans="10:10" ht="12.5">
-      <c r="J708" s="30"/>
+      <c r="J708" s="28"/>
     </row>
     <row r="709" spans="10:10" ht="12.5">
-      <c r="J709" s="30"/>
+      <c r="J709" s="28"/>
     </row>
     <row r="710" spans="10:10" ht="12.5">
-      <c r="J710" s="30"/>
+      <c r="J710" s="28"/>
     </row>
     <row r="711" spans="10:10" ht="12.5">
-      <c r="J711" s="30"/>
+      <c r="J711" s="28"/>
     </row>
     <row r="712" spans="10:10" ht="12.5">
-      <c r="J712" s="30"/>
+      <c r="J712" s="28"/>
     </row>
     <row r="713" spans="10:10" ht="12.5">
-      <c r="J713" s="30"/>
+      <c r="J713" s="28"/>
     </row>
     <row r="714" spans="10:10" ht="12.5">
-      <c r="J714" s="30"/>
+      <c r="J714" s="28"/>
     </row>
     <row r="715" spans="10:10" ht="12.5">
-      <c r="J715" s="30"/>
+      <c r="J715" s="28"/>
     </row>
     <row r="716" spans="10:10" ht="12.5">
-      <c r="J716" s="30"/>
+      <c r="J716" s="28"/>
     </row>
     <row r="717" spans="10:10" ht="12.5">
-      <c r="J717" s="30"/>
+      <c r="J717" s="28"/>
     </row>
     <row r="718" spans="10:10" ht="12.5">
-      <c r="J718" s="30"/>
+      <c r="J718" s="28"/>
     </row>
     <row r="719" spans="10:10" ht="12.5">
-      <c r="J719" s="30"/>
+      <c r="J719" s="28"/>
     </row>
     <row r="720" spans="10:10" ht="12.5">
-      <c r="J720" s="30"/>
+      <c r="J720" s="28"/>
     </row>
     <row r="721" spans="10:10" ht="12.5">
-      <c r="J721" s="30"/>
+      <c r="J721" s="28"/>
     </row>
     <row r="722" spans="10:10" ht="12.5">
-      <c r="J722" s="30"/>
+      <c r="J722" s="28"/>
     </row>
     <row r="723" spans="10:10" ht="12.5">
-      <c r="J723" s="30"/>
+      <c r="J723" s="28"/>
     </row>
     <row r="724" spans="10:10" ht="12.5">
-      <c r="J724" s="30"/>
+      <c r="J724" s="28"/>
     </row>
     <row r="725" spans="10:10" ht="12.5">
-      <c r="J725" s="30"/>
+      <c r="J725" s="28"/>
     </row>
     <row r="726" spans="10:10" ht="12.5">
-      <c r="J726" s="30"/>
+      <c r="J726" s="28"/>
     </row>
     <row r="727" spans="10:10" ht="12.5">
-      <c r="J727" s="30"/>
+      <c r="J727" s="28"/>
     </row>
     <row r="728" spans="10:10" ht="12.5">
-      <c r="J728" s="30"/>
+      <c r="J728" s="28"/>
     </row>
     <row r="729" spans="10:10" ht="12.5">
-      <c r="J729" s="30"/>
+      <c r="J729" s="28"/>
     </row>
     <row r="730" spans="10:10" ht="12.5">
-      <c r="J730" s="30"/>
+      <c r="J730" s="28"/>
     </row>
     <row r="731" spans="10:10" ht="12.5">
-      <c r="J731" s="30"/>
+      <c r="J731" s="28"/>
     </row>
     <row r="732" spans="10:10" ht="12.5">
-      <c r="J732" s="30"/>
+      <c r="J732" s="28"/>
     </row>
     <row r="733" spans="10:10" ht="12.5">
-      <c r="J733" s="30"/>
+      <c r="J733" s="28"/>
     </row>
     <row r="734" spans="10:10" ht="12.5">
-      <c r="J734" s="30"/>
+      <c r="J734" s="28"/>
     </row>
     <row r="735" spans="10:10" ht="12.5">
-      <c r="J735" s="30"/>
+      <c r="J735" s="28"/>
     </row>
     <row r="736" spans="10:10" ht="12.5">
-      <c r="J736" s="30"/>
+      <c r="J736" s="28"/>
     </row>
     <row r="737" spans="10:10" ht="12.5">
-      <c r="J737" s="30"/>
+      <c r="J737" s="28"/>
     </row>
     <row r="738" spans="10:10" ht="12.5">
-      <c r="J738" s="30"/>
+      <c r="J738" s="28"/>
     </row>
     <row r="739" spans="10:10" ht="12.5">
-      <c r="J739" s="30"/>
+      <c r="J739" s="28"/>
     </row>
     <row r="740" spans="10:10" ht="12.5">
-      <c r="J740" s="30"/>
+      <c r="J740" s="28"/>
     </row>
     <row r="741" spans="10:10" ht="12.5">
-      <c r="J741" s="30"/>
+      <c r="J741" s="28"/>
     </row>
     <row r="742" spans="10:10" ht="12.5">
-      <c r="J742" s="30"/>
+      <c r="J742" s="28"/>
     </row>
     <row r="743" spans="10:10" ht="12.5">
-      <c r="J743" s="30"/>
+      <c r="J743" s="28"/>
     </row>
     <row r="744" spans="10:10" ht="12.5">
-      <c r="J744" s="30"/>
+      <c r="J744" s="28"/>
     </row>
     <row r="745" spans="10:10" ht="12.5">
-      <c r="J745" s="30"/>
+      <c r="J745" s="28"/>
     </row>
     <row r="746" spans="10:10" ht="12.5">
-      <c r="J746" s="30"/>
+      <c r="J746" s="28"/>
     </row>
     <row r="747" spans="10:10" ht="12.5">
-      <c r="J747" s="30"/>
+      <c r="J747" s="28"/>
     </row>
     <row r="748" spans="10:10" ht="12.5">
-      <c r="J748" s="30"/>
+      <c r="J748" s="28"/>
     </row>
     <row r="749" spans="10:10" ht="12.5">
-      <c r="J749" s="30"/>
+      <c r="J749" s="28"/>
     </row>
     <row r="750" spans="10:10" ht="12.5">
-      <c r="J750" s="30"/>
+      <c r="J750" s="28"/>
     </row>
     <row r="751" spans="10:10" ht="12.5">
-      <c r="J751" s="30"/>
+      <c r="J751" s="28"/>
     </row>
     <row r="752" spans="10:10" ht="12.5">
-      <c r="J752" s="30"/>
+      <c r="J752" s="28"/>
     </row>
     <row r="753" spans="10:10" ht="12.5">
-      <c r="J753" s="30"/>
+      <c r="J753" s="28"/>
     </row>
     <row r="754" spans="10:10" ht="12.5">
-      <c r="J754" s="30"/>
+      <c r="J754" s="28"/>
     </row>
     <row r="755" spans="10:10" ht="12.5">
-      <c r="J755" s="30"/>
+      <c r="J755" s="28"/>
     </row>
     <row r="756" spans="10:10" ht="12.5">
-      <c r="J756" s="30"/>
+      <c r="J756" s="28"/>
     </row>
     <row r="757" spans="10:10" ht="12.5">
-      <c r="J757" s="30"/>
+      <c r="J757" s="28"/>
     </row>
     <row r="758" spans="10:10" ht="12.5">
-      <c r="J758" s="30"/>
+      <c r="J758" s="28"/>
     </row>
     <row r="759" spans="10:10" ht="12.5">
-      <c r="J759" s="30"/>
+      <c r="J759" s="28"/>
     </row>
     <row r="760" spans="10:10" ht="12.5">
-      <c r="J760" s="30"/>
+      <c r="J760" s="28"/>
     </row>
     <row r="761" spans="10:10" ht="12.5">
-      <c r="J761" s="30"/>
+      <c r="J761" s="28"/>
     </row>
     <row r="762" spans="10:10" ht="12.5">
-      <c r="J762" s="30"/>
+      <c r="J762" s="28"/>
     </row>
     <row r="763" spans="10:10" ht="12.5">
-      <c r="J763" s="30"/>
+      <c r="J763" s="28"/>
     </row>
     <row r="764" spans="10:10" ht="12.5">
-      <c r="J764" s="30"/>
+      <c r="J764" s="28"/>
     </row>
     <row r="765" spans="10:10" ht="12.5">
-      <c r="J765" s="30"/>
+      <c r="J765" s="28"/>
     </row>
     <row r="766" spans="10:10" ht="12.5">
-      <c r="J766" s="30"/>
+      <c r="J766" s="28"/>
     </row>
     <row r="767" spans="10:10" ht="12.5">
-      <c r="J767" s="30"/>
+      <c r="J767" s="28"/>
     </row>
     <row r="768" spans="10:10" ht="12.5">
-      <c r="J768" s="30"/>
+      <c r="J768" s="28"/>
     </row>
     <row r="769" spans="10:10" ht="12.5">
-      <c r="J769" s="30"/>
+      <c r="J769" s="28"/>
     </row>
     <row r="770" spans="10:10" ht="12.5">
-      <c r="J770" s="30"/>
+      <c r="J770" s="28"/>
     </row>
     <row r="771" spans="10:10" ht="12.5">
-      <c r="J771" s="30"/>
+      <c r="J771" s="28"/>
     </row>
     <row r="772" spans="10:10" ht="12.5">
-      <c r="J772" s="30"/>
+      <c r="J772" s="28"/>
     </row>
     <row r="773" spans="10:10" ht="12.5">
-      <c r="J773" s="30"/>
+      <c r="J773" s="28"/>
     </row>
     <row r="774" spans="10:10" ht="12.5">
-      <c r="J774" s="30"/>
+      <c r="J774" s="28"/>
     </row>
     <row r="775" spans="10:10" ht="12.5">
-      <c r="J775" s="30"/>
+      <c r="J775" s="28"/>
     </row>
     <row r="776" spans="10:10" ht="12.5">
-      <c r="J776" s="30"/>
+      <c r="J776" s="28"/>
     </row>
     <row r="777" spans="10:10" ht="12.5">
-      <c r="J777" s="30"/>
+      <c r="J777" s="28"/>
     </row>
     <row r="778" spans="10:10" ht="12.5">
-      <c r="J778" s="30"/>
+      <c r="J778" s="28"/>
     </row>
     <row r="779" spans="10:10" ht="12.5">
-      <c r="J779" s="30"/>
+      <c r="J779" s="28"/>
     </row>
     <row r="780" spans="10:10" ht="12.5">
-      <c r="J780" s="30"/>
+      <c r="J780" s="28"/>
     </row>
     <row r="781" spans="10:10" ht="12.5">
-      <c r="J781" s="30"/>
+      <c r="J781" s="28"/>
     </row>
     <row r="782" spans="10:10" ht="12.5">
-      <c r="J782" s="30"/>
+      <c r="J782" s="28"/>
     </row>
     <row r="783" spans="10:10" ht="12.5">
-      <c r="J783" s="30"/>
+      <c r="J783" s="28"/>
     </row>
     <row r="784" spans="10:10" ht="12.5">
-      <c r="J784" s="30"/>
+      <c r="J784" s="28"/>
     </row>
     <row r="785" spans="10:10" ht="12.5">
-      <c r="J785" s="30"/>
+      <c r="J785" s="28"/>
     </row>
     <row r="786" spans="10:10" ht="12.5">
-      <c r="J786" s="30"/>
+      <c r="J786" s="28"/>
     </row>
     <row r="787" spans="10:10" ht="12.5">
-      <c r="J787" s="30"/>
+      <c r="J787" s="28"/>
     </row>
     <row r="788" spans="10:10" ht="12.5">
-      <c r="J788" s="30"/>
+      <c r="J788" s="28"/>
     </row>
     <row r="789" spans="10:10" ht="12.5">
-      <c r="J789" s="30"/>
+      <c r="J789" s="28"/>
     </row>
     <row r="790" spans="10:10" ht="12.5">
-      <c r="J790" s="30"/>
+      <c r="J790" s="28"/>
     </row>
     <row r="791" spans="10:10" ht="12.5">
-      <c r="J791" s="30"/>
+      <c r="J791" s="28"/>
     </row>
     <row r="792" spans="10:10" ht="12.5">
-      <c r="J792" s="30"/>
+      <c r="J792" s="28"/>
     </row>
     <row r="793" spans="10:10" ht="12.5">
-      <c r="J793" s="30"/>
+      <c r="J793" s="28"/>
     </row>
     <row r="794" spans="10:10" ht="12.5">
-      <c r="J794" s="30"/>
+      <c r="J794" s="28"/>
     </row>
     <row r="795" spans="10:10" ht="12.5">
-      <c r="J795" s="30"/>
+      <c r="J795" s="28"/>
     </row>
     <row r="796" spans="10:10" ht="12.5">
-      <c r="J796" s="30"/>
+      <c r="J796" s="28"/>
     </row>
     <row r="797" spans="10:10" ht="12.5">
-      <c r="J797" s="30"/>
+      <c r="J797" s="28"/>
     </row>
     <row r="798" spans="10:10" ht="12.5">
-      <c r="J798" s="30"/>
+      <c r="J798" s="28"/>
     </row>
     <row r="799" spans="10:10" ht="12.5">
-      <c r="J799" s="30"/>
+      <c r="J799" s="28"/>
     </row>
     <row r="800" spans="10:10" ht="12.5">
-      <c r="J800" s="30"/>
+      <c r="J800" s="28"/>
     </row>
     <row r="801" spans="10:10" ht="12.5">
-      <c r="J801" s="30"/>
+      <c r="J801" s="28"/>
     </row>
     <row r="802" spans="10:10" ht="12.5">
-      <c r="J802" s="30"/>
+      <c r="J802" s="28"/>
     </row>
     <row r="803" spans="10:10" ht="12.5">
-      <c r="J803" s="30"/>
+      <c r="J803" s="28"/>
     </row>
     <row r="804" spans="10:10" ht="12.5">
-      <c r="J804" s="30"/>
+      <c r="J804" s="28"/>
     </row>
     <row r="805" spans="10:10" ht="12.5">
-      <c r="J805" s="30"/>
+      <c r="J805" s="28"/>
     </row>
     <row r="806" spans="10:10" ht="12.5">
-      <c r="J806" s="30"/>
+      <c r="J806" s="28"/>
     </row>
     <row r="807" spans="10:10" ht="12.5">
-      <c r="J807" s="30"/>
+      <c r="J807" s="28"/>
     </row>
     <row r="808" spans="10:10" ht="12.5">
-      <c r="J808" s="30"/>
+      <c r="J808" s="28"/>
     </row>
     <row r="809" spans="10:10" ht="12.5">
-      <c r="J809" s="30"/>
+      <c r="J809" s="28"/>
     </row>
     <row r="810" spans="10:10" ht="12.5">
-      <c r="J810" s="30"/>
+      <c r="J810" s="28"/>
     </row>
     <row r="811" spans="10:10" ht="12.5">
-      <c r="J811" s="30"/>
+      <c r="J811" s="28"/>
     </row>
     <row r="812" spans="10:10" ht="12.5">
-      <c r="J812" s="30"/>
+      <c r="J812" s="28"/>
     </row>
     <row r="813" spans="10:10" ht="12.5">
-      <c r="J813" s="30"/>
+      <c r="J813" s="28"/>
     </row>
     <row r="814" spans="10:10" ht="12.5">
-      <c r="J814" s="30"/>
+      <c r="J814" s="28"/>
     </row>
     <row r="815" spans="10:10" ht="12.5">
-      <c r="J815" s="30"/>
+      <c r="J815" s="28"/>
     </row>
     <row r="816" spans="10:10" ht="12.5">
-      <c r="J816" s="30"/>
+      <c r="J816" s="28"/>
     </row>
     <row r="817" spans="10:10" ht="12.5">
-      <c r="J817" s="30"/>
+      <c r="J817" s="28"/>
     </row>
     <row r="818" spans="10:10" ht="12.5">
-      <c r="J818" s="30"/>
+      <c r="J818" s="28"/>
     </row>
     <row r="819" spans="10:10" ht="12.5">
-      <c r="J819" s="30"/>
+      <c r="J819" s="28"/>
     </row>
     <row r="820" spans="10:10" ht="12.5">
-      <c r="J820" s="30"/>
+      <c r="J820" s="28"/>
     </row>
     <row r="821" spans="10:10" ht="12.5">
-      <c r="J821" s="30"/>
+      <c r="J821" s="28"/>
     </row>
     <row r="822" spans="10:10" ht="12.5">
-      <c r="J822" s="30"/>
+      <c r="J822" s="28"/>
     </row>
     <row r="823" spans="10:10" ht="12.5">
-      <c r="J823" s="30"/>
+      <c r="J823" s="28"/>
     </row>
     <row r="824" spans="10:10" ht="12.5">
-      <c r="J824" s="30"/>
+      <c r="J824" s="28"/>
     </row>
     <row r="825" spans="10:10" ht="12.5">
-      <c r="J825" s="30"/>
+      <c r="J825" s="28"/>
     </row>
     <row r="826" spans="10:10" ht="12.5">
-      <c r="J826" s="30"/>
+      <c r="J826" s="28"/>
     </row>
     <row r="827" spans="10:10" ht="12.5">
-      <c r="J827" s="30"/>
+      <c r="J827" s="28"/>
     </row>
     <row r="828" spans="10:10" ht="12.5">
-      <c r="J828" s="30"/>
+      <c r="J828" s="28"/>
     </row>
     <row r="829" spans="10:10" ht="12.5">
-      <c r="J829" s="30"/>
+      <c r="J829" s="28"/>
     </row>
     <row r="830" spans="10:10" ht="12.5">
-      <c r="J830" s="30"/>
+      <c r="J830" s="28"/>
     </row>
     <row r="831" spans="10:10" ht="12.5">
-      <c r="J831" s="30"/>
+      <c r="J831" s="28"/>
     </row>
     <row r="832" spans="10:10" ht="12.5">
-      <c r="J832" s="30"/>
+      <c r="J832" s="28"/>
     </row>
     <row r="833" spans="10:10" ht="12.5">
-      <c r="J833" s="30"/>
+      <c r="J833" s="28"/>
     </row>
     <row r="834" spans="10:10" ht="12.5">
-      <c r="J834" s="30"/>
+      <c r="J834" s="28"/>
     </row>
     <row r="835" spans="10:10" ht="12.5">
-      <c r="J835" s="30"/>
+      <c r="J835" s="28"/>
     </row>
     <row r="836" spans="10:10" ht="12.5">
-      <c r="J836" s="30"/>
+      <c r="J836" s="28"/>
     </row>
     <row r="837" spans="10:10" ht="12.5">
-      <c r="J837" s="30"/>
+      <c r="J837" s="28"/>
     </row>
     <row r="838" spans="10:10" ht="12.5">
-      <c r="J838" s="30"/>
+      <c r="J838" s="28"/>
     </row>
     <row r="839" spans="10:10" ht="12.5">
-      <c r="J839" s="30"/>
+      <c r="J839" s="28"/>
     </row>
     <row r="840" spans="10:10" ht="12.5">
-      <c r="J840" s="30"/>
+      <c r="J840" s="28"/>
     </row>
     <row r="841" spans="10:10" ht="12.5">
-      <c r="J841" s="30"/>
+      <c r="J841" s="28"/>
     </row>
     <row r="842" spans="10:10" ht="12.5">
-      <c r="J842" s="30"/>
+      <c r="J842" s="28"/>
     </row>
     <row r="843" spans="10:10" ht="12.5">
-      <c r="J843" s="30"/>
+      <c r="J843" s="28"/>
     </row>
     <row r="844" spans="10:10" ht="12.5">
-      <c r="J844" s="30"/>
+      <c r="J844" s="28"/>
     </row>
     <row r="845" spans="10:10" ht="12.5">
-      <c r="J845" s="30"/>
+      <c r="J845" s="28"/>
     </row>
     <row r="846" spans="10:10" ht="12.5">
-      <c r="J846" s="30"/>
+      <c r="J846" s="28"/>
     </row>
     <row r="847" spans="10:10" ht="12.5">
-      <c r="J847" s="30"/>
+      <c r="J847" s="28"/>
     </row>
     <row r="848" spans="10:10" ht="12.5">
-      <c r="J848" s="30"/>
+      <c r="J848" s="28"/>
     </row>
     <row r="849" spans="10:10" ht="12.5">
-      <c r="J849" s="30"/>
+      <c r="J849" s="28"/>
     </row>
     <row r="850" spans="10:10" ht="12.5">
-      <c r="J850" s="30"/>
+      <c r="J850" s="28"/>
     </row>
     <row r="851" spans="10:10" ht="12.5">
-      <c r="J851" s="30"/>
+      <c r="J851" s="28"/>
     </row>
     <row r="852" spans="10:10" ht="12.5">
-      <c r="J852" s="30"/>
+      <c r="J852" s="28"/>
     </row>
     <row r="853" spans="10:10" ht="12.5">
-      <c r="J853" s="30"/>
+      <c r="J853" s="28"/>
     </row>
     <row r="854" spans="10:10" ht="12.5">
-      <c r="J854" s="30"/>
+      <c r="J854" s="28"/>
     </row>
     <row r="855" spans="10:10" ht="12.5">
-      <c r="J855" s="30"/>
+      <c r="J855" s="28"/>
     </row>
     <row r="856" spans="10:10" ht="12.5">
-      <c r="J856" s="30"/>
+      <c r="J856" s="28"/>
     </row>
     <row r="857" spans="10:10" ht="12.5">
-      <c r="J857" s="30"/>
+      <c r="J857" s="28"/>
     </row>
     <row r="858" spans="10:10" ht="12.5">
-      <c r="J858" s="30"/>
+      <c r="J858" s="28"/>
     </row>
     <row r="859" spans="10:10" ht="12.5">
-      <c r="J859" s="30"/>
+      <c r="J859" s="28"/>
     </row>
     <row r="860" spans="10:10" ht="12.5">
-      <c r="J860" s="30"/>
+      <c r="J860" s="28"/>
     </row>
     <row r="861" spans="10:10" ht="12.5">
-      <c r="J861" s="30"/>
+      <c r="J861" s="28"/>
     </row>
     <row r="862" spans="10:10" ht="12.5">
-      <c r="J862" s="30"/>
+      <c r="J862" s="28"/>
     </row>
     <row r="863" spans="10:10" ht="12.5">
-      <c r="J863" s="30"/>
+      <c r="J863" s="28"/>
     </row>
     <row r="864" spans="10:10" ht="12.5">
-      <c r="J864" s="30"/>
+      <c r="J864" s="28"/>
     </row>
     <row r="865" spans="10:10" ht="12.5">
-      <c r="J865" s="30"/>
+      <c r="J865" s="28"/>
     </row>
     <row r="866" spans="10:10" ht="12.5">
-      <c r="J866" s="30"/>
+      <c r="J866" s="28"/>
     </row>
     <row r="867" spans="10:10" ht="12.5">
-      <c r="J867" s="30"/>
+      <c r="J867" s="28"/>
     </row>
     <row r="868" spans="10:10" ht="12.5">
-      <c r="J868" s="30"/>
+      <c r="J868" s="28"/>
     </row>
     <row r="869" spans="10:10" ht="12.5">
-      <c r="J869" s="30"/>
+      <c r="J869" s="28"/>
     </row>
     <row r="870" spans="10:10" ht="12.5">
-      <c r="J870" s="30"/>
+      <c r="J870" s="28"/>
     </row>
     <row r="871" spans="10:10" ht="12.5">
-      <c r="J871" s="30"/>
+      <c r="J871" s="28"/>
     </row>
     <row r="872" spans="10:10" ht="12.5">
-      <c r="J872" s="30"/>
+      <c r="J872" s="28"/>
     </row>
     <row r="873" spans="10:10" ht="12.5">
-      <c r="J873" s="30"/>
+      <c r="J873" s="28"/>
     </row>
     <row r="874" spans="10:10" ht="12.5">
-      <c r="J874" s="30"/>
+      <c r="J874" s="28"/>
     </row>
     <row r="875" spans="10:10" ht="12.5">
-      <c r="J875" s="30"/>
+      <c r="J875" s="28"/>
     </row>
     <row r="876" spans="10:10" ht="12.5">
-      <c r="J876" s="30"/>
+      <c r="J876" s="28"/>
     </row>
     <row r="877" spans="10:10" ht="12.5">
-      <c r="J877" s="30"/>
+      <c r="J877" s="28"/>
     </row>
     <row r="878" spans="10:10" ht="12.5">
-      <c r="J878" s="30"/>
+      <c r="J878" s="28"/>
     </row>
     <row r="879" spans="10:10" ht="12.5">
-      <c r="J879" s="30"/>
+      <c r="J879" s="28"/>
     </row>
     <row r="880" spans="10:10" ht="12.5">
-      <c r="J880" s="30"/>
+      <c r="J880" s="28"/>
     </row>
     <row r="881" spans="10:10" ht="12.5">
-      <c r="J881" s="30"/>
+      <c r="J881" s="28"/>
     </row>
     <row r="882" spans="10:10" ht="12.5">
-      <c r="J882" s="30"/>
+      <c r="J882" s="28"/>
     </row>
     <row r="883" spans="10:10" ht="12.5">
-      <c r="J883" s="30"/>
+      <c r="J883" s="28"/>
     </row>
     <row r="884" spans="10:10" ht="12.5">
-      <c r="J884" s="30"/>
+      <c r="J884" s="28"/>
     </row>
     <row r="885" spans="10:10" ht="12.5">
-      <c r="J885" s="30"/>
+      <c r="J885" s="28"/>
     </row>
     <row r="886" spans="10:10" ht="12.5">
-      <c r="J886" s="30"/>
+      <c r="J886" s="28"/>
     </row>
     <row r="887" spans="10:10" ht="12.5">
-      <c r="J887" s="30"/>
+      <c r="J887" s="28"/>
     </row>
     <row r="888" spans="10:10" ht="12.5">
-      <c r="J888" s="30"/>
+      <c r="J888" s="28"/>
     </row>
     <row r="889" spans="10:10" ht="12.5">
-      <c r="J889" s="30"/>
+      <c r="J889" s="28"/>
     </row>
     <row r="890" spans="10:10" ht="12.5">
-      <c r="J890" s="30"/>
+      <c r="J890" s="28"/>
     </row>
     <row r="891" spans="10:10" ht="12.5">
-      <c r="J891" s="30"/>
+      <c r="J891" s="28"/>
     </row>
     <row r="892" spans="10:10" ht="12.5">
-      <c r="J892" s="30"/>
+      <c r="J892" s="28"/>
     </row>
     <row r="893" spans="10:10" ht="12.5">
-      <c r="J893" s="30"/>
+      <c r="J893" s="28"/>
     </row>
     <row r="894" spans="10:10" ht="12.5">
-      <c r="J894" s="30"/>
+      <c r="J894" s="28"/>
     </row>
     <row r="895" spans="10:10" ht="12.5">
-      <c r="J895" s="30"/>
+      <c r="J895" s="28"/>
     </row>
     <row r="896" spans="10:10" ht="12.5">
-      <c r="J896" s="30"/>
+      <c r="J896" s="28"/>
     </row>
     <row r="897" spans="10:10" ht="12.5">
-      <c r="J897" s="30"/>
+      <c r="J897" s="28"/>
     </row>
     <row r="898" spans="10:10" ht="12.5">
-      <c r="J898" s="30"/>
+      <c r="J898" s="28"/>
     </row>
     <row r="899" spans="10:10" ht="12.5">
-      <c r="J899" s="30"/>
+      <c r="J899" s="28"/>
     </row>
     <row r="900" spans="10:10" ht="12.5">
-      <c r="J900" s="30"/>
+      <c r="J900" s="28"/>
     </row>
     <row r="901" spans="10:10" ht="12.5">
-      <c r="J901" s="30"/>
+      <c r="J901" s="28"/>
     </row>
     <row r="902" spans="10:10" ht="12.5">
-      <c r="J902" s="30"/>
+      <c r="J902" s="28"/>
     </row>
     <row r="903" spans="10:10" ht="12.5">
-      <c r="J903" s="30"/>
+      <c r="J903" s="28"/>
     </row>
     <row r="904" spans="10:10" ht="12.5">
-      <c r="J904" s="30"/>
+      <c r="J904" s="28"/>
     </row>
     <row r="905" spans="10:10" ht="12.5">
-      <c r="J905" s="30"/>
+      <c r="J905" s="28"/>
     </row>
     <row r="906" spans="10:10" ht="12.5">
-      <c r="J906" s="30"/>
+      <c r="J906" s="28"/>
     </row>
     <row r="907" spans="10:10" ht="12.5">
-      <c r="J907" s="30"/>
+      <c r="J907" s="28"/>
     </row>
     <row r="908" spans="10:10" ht="12.5">
-      <c r="J908" s="30"/>
+      <c r="J908" s="28"/>
     </row>
     <row r="909" spans="10:10" ht="12.5">
-      <c r="J909" s="30"/>
+      <c r="J909" s="28"/>
     </row>
     <row r="910" spans="10:10" ht="12.5">
-      <c r="J910" s="30"/>
+      <c r="J910" s="28"/>
     </row>
     <row r="911" spans="10:10" ht="12.5">
-      <c r="J911" s="30"/>
+      <c r="J911" s="28"/>
     </row>
     <row r="912" spans="10:10" ht="12.5">
-      <c r="J912" s="30"/>
+      <c r="J912" s="28"/>
     </row>
     <row r="913" spans="10:10" ht="12.5">
-      <c r="J913" s="30"/>
+      <c r="J913" s="28"/>
     </row>
     <row r="914" spans="10:10" ht="12.5">
-      <c r="J914" s="30"/>
+      <c r="J914" s="28"/>
     </row>
     <row r="915" spans="10:10" ht="12.5">
-      <c r="J915" s="30"/>
+      <c r="J915" s="28"/>
     </row>
     <row r="916" spans="10:10" ht="12.5">
-      <c r="J916" s="30"/>
+      <c r="J916" s="28"/>
     </row>
     <row r="917" spans="10:10" ht="12.5">
-      <c r="J917" s="30"/>
+      <c r="J917" s="28"/>
     </row>
     <row r="918" spans="10:10" ht="12.5">
-      <c r="J918" s="30"/>
+      <c r="J918" s="28"/>
     </row>
     <row r="919" spans="10:10" ht="12.5">
-      <c r="J919" s="30"/>
+      <c r="J919" s="28"/>
     </row>
     <row r="920" spans="10:10" ht="12.5">
-      <c r="J920" s="30"/>
+      <c r="J920" s="28"/>
     </row>
     <row r="921" spans="10:10" ht="12.5">
-      <c r="J921" s="30"/>
+      <c r="J921" s="28"/>
     </row>
     <row r="922" spans="10:10" ht="12.5">
-      <c r="J922" s="30"/>
+      <c r="J922" s="28"/>
     </row>
     <row r="923" spans="10:10" ht="12.5">
-      <c r="J923" s="30"/>
+      <c r="J923" s="28"/>
     </row>
     <row r="924" spans="10:10" ht="12.5">
-      <c r="J924" s="30"/>
+      <c r="J924" s="28"/>
     </row>
     <row r="925" spans="10:10" ht="12.5">
-      <c r="J925" s="30"/>
+      <c r="J925" s="28"/>
     </row>
     <row r="926" spans="10:10" ht="12.5">
-      <c r="J926" s="30"/>
+      <c r="J926" s="28"/>
     </row>
     <row r="927" spans="10:10" ht="12.5">
-      <c r="J927" s="30"/>
+      <c r="J927" s="28"/>
     </row>
     <row r="928" spans="10:10" ht="12.5">
-      <c r="J928" s="30"/>
+      <c r="J928" s="28"/>
     </row>
     <row r="929" spans="10:10" ht="12.5">
-      <c r="J929" s="30"/>
+      <c r="J929" s="28"/>
     </row>
     <row r="930" spans="10:10" ht="12.5">
-      <c r="J930" s="30"/>
+      <c r="J930" s="28"/>
     </row>
     <row r="931" spans="10:10" ht="12.5">
-      <c r="J931" s="30"/>
+      <c r="J931" s="28"/>
     </row>
     <row r="932" spans="10:10" ht="12.5">
-      <c r="J932" s="30"/>
+      <c r="J932" s="28"/>
     </row>
     <row r="933" spans="10:10" ht="12.5">
-      <c r="J933" s="30"/>
+      <c r="J933" s="28"/>
     </row>
     <row r="934" spans="10:10" ht="12.5">
-      <c r="J934" s="30"/>
+      <c r="J934" s="28"/>
     </row>
     <row r="935" spans="10:10" ht="12.5">
-      <c r="J935" s="30"/>
+      <c r="J935" s="28"/>
     </row>
     <row r="936" spans="10:10" ht="12.5">
-      <c r="J936" s="30"/>
+      <c r="J936" s="28"/>
     </row>
     <row r="937" spans="10:10" ht="12.5">
-      <c r="J937" s="30"/>
+      <c r="J937" s="28"/>
     </row>
     <row r="938" spans="10:10" ht="12.5">
-      <c r="J938" s="30"/>
+      <c r="J938" s="28"/>
     </row>
     <row r="939" spans="10:10" ht="12.5">
-      <c r="J939" s="30"/>
+      <c r="J939" s="28"/>
     </row>
     <row r="940" spans="10:10" ht="12.5">
-      <c r="J940" s="30"/>
+      <c r="J940" s="28"/>
     </row>
     <row r="941" spans="10:10" ht="12.5">
-      <c r="J941" s="30"/>
+      <c r="J941" s="28"/>
     </row>
     <row r="942" spans="10:10" ht="12.5">
-      <c r="J942" s="30"/>
+      <c r="J942" s="28"/>
     </row>
     <row r="943" spans="10:10" ht="12.5">
-      <c r="J943" s="30"/>
+      <c r="J943" s="28"/>
     </row>
     <row r="944" spans="10:10" ht="12.5">
-      <c r="J944" s="30"/>
+      <c r="J944" s="28"/>
     </row>
     <row r="945" spans="10:10" ht="12.5">
-      <c r="J945" s="30"/>
+      <c r="J945" s="28"/>
     </row>
     <row r="946" spans="10:10" ht="12.5">
-      <c r="J946" s="30"/>
+      <c r="J946" s="28"/>
     </row>
     <row r="947" spans="10:10" ht="12.5">
-      <c r="J947" s="30"/>
+      <c r="J947" s="28"/>
     </row>
     <row r="948" spans="10:10" ht="12.5">
-      <c r="J948" s="30"/>
+      <c r="J948" s="28"/>
     </row>
     <row r="949" spans="10:10" ht="12.5">
-      <c r="J949" s="30"/>
+      <c r="J949" s="28"/>
     </row>
     <row r="950" spans="10:10" ht="12.5">
-      <c r="J950" s="30"/>
+      <c r="J950" s="28"/>
     </row>
     <row r="951" spans="10:10" ht="12.5">
-      <c r="J951" s="30"/>
+      <c r="J951" s="28"/>
     </row>
     <row r="952" spans="10:10" ht="12.5">
-      <c r="J952" s="30"/>
+      <c r="J952" s="28"/>
     </row>
     <row r="953" spans="10:10" ht="12.5">
-      <c r="J953" s="30"/>
+      <c r="J953" s="28"/>
     </row>
     <row r="954" spans="10:10" ht="12.5">
-      <c r="J954" s="30"/>
+      <c r="J954" s="28"/>
     </row>
     <row r="955" spans="10:10" ht="12.5">
-      <c r="J955" s="30"/>
+      <c r="J955" s="28"/>
     </row>
     <row r="956" spans="10:10" ht="12.5">
-      <c r="J956" s="30"/>
+      <c r="J956" s="28"/>
     </row>
     <row r="957" spans="10:10" ht="12.5">
-      <c r="J957" s="30"/>
+      <c r="J957" s="28"/>
     </row>
     <row r="958" spans="10:10" ht="12.5">
-      <c r="J958" s="30"/>
+      <c r="J958" s="28"/>
     </row>
     <row r="959" spans="10:10" ht="12.5">
-      <c r="J959" s="30"/>
+      <c r="J959" s="28"/>
     </row>
     <row r="960" spans="10:10" ht="12.5">
-      <c r="J960" s="30"/>
+      <c r="J960" s="28"/>
     </row>
     <row r="961" spans="10:10" ht="12.5">
-      <c r="J961" s="30"/>
+      <c r="J961" s="28"/>
     </row>
     <row r="962" spans="10:10" ht="12.5">
-      <c r="J962" s="30"/>
+      <c r="J962" s="28"/>
     </row>
     <row r="963" spans="10:10" ht="12.5">
-      <c r="J963" s="30"/>
+      <c r="J963" s="28"/>
     </row>
     <row r="964" spans="10:10" ht="12.5">
-      <c r="J964" s="30"/>
+      <c r="J964" s="28"/>
     </row>
     <row r="965" spans="10:10" ht="12.5">
-      <c r="J965" s="30"/>
+      <c r="J965" s="28"/>
     </row>
     <row r="966" spans="10:10" ht="12.5">
-      <c r="J966" s="30"/>
+      <c r="J966" s="28"/>
     </row>
     <row r="967" spans="10:10" ht="12.5">
-      <c r="J967" s="30"/>
+      <c r="J967" s="28"/>
     </row>
     <row r="968" spans="10:10" ht="12.5">
-      <c r="J968" s="30"/>
+      <c r="J968" s="28"/>
     </row>
     <row r="969" spans="10:10" ht="12.5">
-      <c r="J969" s="30"/>
+      <c r="J969" s="28"/>
     </row>
     <row r="970" spans="10:10" ht="12.5">
-      <c r="J970" s="30"/>
+      <c r="J970" s="28"/>
     </row>
     <row r="971" spans="10:10" ht="12.5">
-      <c r="J971" s="30"/>
+      <c r="J971" s="28"/>
     </row>
     <row r="972" spans="10:10" ht="12.5">
-      <c r="J972" s="30"/>
+      <c r="J972" s="28"/>
     </row>
     <row r="973" spans="10:10" ht="12.5">
-      <c r="J973" s="30"/>
+      <c r="J973" s="28"/>
     </row>
     <row r="974" spans="10:10" ht="12.5">
-      <c r="J974" s="30"/>
+      <c r="J974" s="28"/>
     </row>
     <row r="975" spans="10:10" ht="12.5">
-      <c r="J975" s="30"/>
+      <c r="J975" s="28"/>
     </row>
     <row r="976" spans="10:10" ht="12.5">
-      <c r="J976" s="30"/>
+      <c r="J976" s="28"/>
     </row>
     <row r="977" spans="10:10" ht="12.5">
-      <c r="J977" s="30"/>
+      <c r="J977" s="28"/>
     </row>
     <row r="978" spans="10:10" ht="12.5">
-      <c r="J978" s="30"/>
+      <c r="J978" s="28"/>
     </row>
     <row r="979" spans="10:10" ht="12.5">
-      <c r="J979" s="30"/>
+      <c r="J979" s="28"/>
     </row>
     <row r="980" spans="10:10" ht="12.5">
-      <c r="J980" s="30"/>
+      <c r="J980" s="28"/>
     </row>
     <row r="981" spans="10:10" ht="12.5">
-      <c r="J981" s="30"/>
+      <c r="J981" s="28"/>
     </row>
     <row r="982" spans="10:10" ht="12.5">
-      <c r="J982" s="30"/>
+      <c r="J982" s="28"/>
     </row>
     <row r="983" spans="10:10" ht="12.5">
-      <c r="J983" s="30"/>
+      <c r="J983" s="28"/>
     </row>
     <row r="984" spans="10:10" ht="12.5">
-      <c r="J984" s="30"/>
+      <c r="J984" s="28"/>
     </row>
     <row r="985" spans="10:10" ht="12.5">
-      <c r="J985" s="30"/>
+      <c r="J985" s="28"/>
     </row>
     <row r="986" spans="10:10" ht="12.5">
-      <c r="J986" s="30"/>
+      <c r="J986" s="28"/>
     </row>
     <row r="987" spans="10:10" ht="12.5">
-      <c r="J987" s="30"/>
+      <c r="J987" s="28"/>
     </row>
     <row r="988" spans="10:10" ht="12.5">
-      <c r="J988" s="30"/>
+      <c r="J988" s="28"/>
     </row>
     <row r="989" spans="10:10" ht="12.5">
-      <c r="J989" s="30"/>
+      <c r="J989" s="28"/>
     </row>
     <row r="990" spans="10:10" ht="12.5">
-      <c r="J990" s="30"/>
+      <c r="J990" s="28"/>
     </row>
     <row r="991" spans="10:10" ht="12.5">
-      <c r="J991" s="30"/>
+      <c r="J991" s="28"/>
     </row>
     <row r="992" spans="10:10" ht="12.5">
-      <c r="J992" s="30"/>
+      <c r="J992" s="28"/>
     </row>
     <row r="993" spans="10:10" ht="12.5">
-      <c r="J993" s="30"/>
+      <c r="J993" s="28"/>
     </row>
     <row r="994" spans="10:10" ht="12.5">
-      <c r="J994" s="30"/>
+      <c r="J994" s="28"/>
     </row>
     <row r="995" spans="10:10" ht="12.5">
-      <c r="J995" s="30"/>
+      <c r="J995" s="28"/>
     </row>
     <row r="996" spans="10:10" ht="12.5">
-      <c r="J996" s="30"/>
+      <c r="J996" s="28"/>
     </row>
     <row r="997" spans="10:10" ht="12.5">
-      <c r="J997" s="30"/>
+      <c r="J997" s="28"/>
     </row>
     <row r="998" spans="10:10" ht="12.5">
-      <c r="J998" s="30"/>
+      <c r="J998" s="28"/>
     </row>
     <row r="999" spans="10:10" ht="12.5">
-      <c r="J999" s="30"/>
+      <c r="J999" s="28"/>
     </row>
     <row r="1000" spans="10:10" ht="12.5">
-      <c r="J1000" s="30"/>
+      <c r="J1000" s="28"/>
     </row>
     <row r="1001" spans="10:10" ht="12.5">
-      <c r="J1001" s="30"/>
+      <c r="J1001" s="28"/>
     </row>
     <row r="1002" spans="10:10" ht="12.5">
-      <c r="J1002" s="30"/>
+      <c r="J1002" s="28"/>
     </row>
     <row r="1003" spans="10:10" ht="12.5">
-      <c r="J1003" s="30"/>
+      <c r="J1003" s="28"/>
     </row>
     <row r="1004" spans="10:10" ht="12.5">
-      <c r="J1004" s="30"/>
+      <c r="J1004" s="28"/>
     </row>
     <row r="1005" spans="10:10" ht="12.5">
-      <c r="J1005" s="30"/>
+      <c r="J1005" s="28"/>
     </row>
     <row r="1006" spans="10:10" ht="12.5">
-      <c r="J1006" s="30"/>
+      <c r="J1006" s="28"/>
     </row>
     <row r="1007" spans="10:10" ht="12.5">
-      <c r="J1007" s="30"/>
+      <c r="J1007" s="28"/>
     </row>
     <row r="1008" spans="10:10" ht="12.5">
-      <c r="J1008" s="30"/>
+      <c r="J1008" s="28"/>
     </row>
     <row r="1009" spans="10:10" ht="12.5">
-      <c r="J1009" s="30"/>
+      <c r="J1009" s="28"/>
     </row>
     <row r="1010" spans="10:10" ht="12.5">
-      <c r="J1010" s="30"/>
+      <c r="J1010" s="28"/>
     </row>
     <row r="1011" spans="10:10" ht="12.5">
-      <c r="J1011" s="30"/>
+      <c r="J1011" s="28"/>
     </row>
     <row r="1012" spans="10:10" ht="12.5">
-      <c r="J1012" s="30"/>
+      <c r="J1012" s="28"/>
     </row>
     <row r="1013" spans="10:10" ht="12.5">
-      <c r="J1013" s="30"/>
+      <c r="J1013" s="28"/>
     </row>
     <row r="1014" spans="10:10" ht="12.5">
-      <c r="J1014" s="30"/>
+      <c r="J1014" s="28"/>
     </row>
     <row r="1015" spans="10:10" ht="12.5">
-      <c r="J1015" s="30"/>
+      <c r="J1015" s="28"/>
     </row>
     <row r="1016" spans="10:10" ht="12.5">
-      <c r="J1016" s="30"/>
+      <c r="J1016" s="28"/>
     </row>
     <row r="1017" spans="10:10" ht="12.5">
-      <c r="J1017" s="30"/>
+      <c r="J1017" s="28"/>
     </row>
     <row r="1018" spans="10:10" ht="12.5">
-      <c r="J1018" s="30"/>
+      <c r="J1018" s="28"/>
     </row>
     <row r="1019" spans="10:10" ht="12.5">
-      <c r="J1019" s="30"/>
+      <c r="J1019" s="28"/>
     </row>
     <row r="1020" spans="10:10" ht="12.5">
-      <c r="J1020" s="30"/>
+      <c r="J1020" s="28"/>
     </row>
     <row r="1021" spans="10:10" ht="12.5">
-      <c r="J1021" s="30"/>
+      <c r="J1021" s="28"/>
     </row>
     <row r="1022" spans="10:10" ht="12.5">
-      <c r="J1022" s="30"/>
+      <c r="J1022" s="28"/>
     </row>
     <row r="1023" spans="10:10" ht="12.5">
-      <c r="J1023" s="30"/>
+      <c r="J1023" s="28"/>
     </row>
     <row r="1024" spans="10:10" ht="12.5">
-      <c r="J1024" s="30"/>
+      <c r="J1024" s="28"/>
     </row>
     <row r="1025" spans="10:10" ht="12.5">
-      <c r="J1025" s="30"/>
+      <c r="J1025" s="28"/>
     </row>
     <row r="1026" spans="10:10" ht="12.5">
-      <c r="J1026" s="30"/>
+      <c r="J1026" s="28"/>
     </row>
     <row r="1027" spans="10:10" ht="12.5">
-      <c r="J1027" s="30"/>
-    </row>
-    <row r="1028" spans="10:10" ht="12.5">
-      <c r="J1028" s="30"/>
+      <c r="J1027" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="65">
+    <mergeCell ref="C46:E46"/>
     <mergeCell ref="C47:E47"/>
     <mergeCell ref="C48:E48"/>
     <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C41:E41"/>
     <mergeCell ref="C42:E42"/>
     <mergeCell ref="C43:E43"/>
     <mergeCell ref="C44:E44"/>
     <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="C37:E37"/>
     <mergeCell ref="C38:E38"/>
     <mergeCell ref="C39:E39"/>
     <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="D27:E27"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="D30:E30"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C25:E25"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="D18:E18"/>
@@ -6541,22 +6645,22 @@
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C4:E4"/>
+    <mergeCell ref="D55:E55"/>
     <mergeCell ref="D56:E56"/>
-    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="C66:E66"/>
     <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C57:E57"/>
     <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="D59:E59"/>
     <mergeCell ref="D60:E60"/>
     <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="C64:E64"/>
     <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="D50:E50"/>
     <mergeCell ref="D51:E51"/>
     <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="D54:E54"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -6588,41 +6692,40 @@
     <hyperlink ref="J21" r:id="rId27" location="5073" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
     <hyperlink ref="J23" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
     <hyperlink ref="J24" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="J25" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="J26" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="J28" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="J29" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="J31" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="J32" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="J35" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="J36" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="J37" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="J38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="J39" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="J40" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="J41" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="J42" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="J43" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="J44" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="J45" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="J46" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="J47" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="J48" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="J49" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="J51" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="J52" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="J53" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="J55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="J56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="J57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="J58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="J60" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="J61" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="J63" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="J64" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="J66" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="J67" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="J68" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="J25" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="J27" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="J28" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="J30" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="J31" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="J34" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="J35" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="J36" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="J37" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="J38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="J39" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="J40" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="J41" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="J42" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="J43" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="J44" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="J45" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="J46" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="J47" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="J48" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="J50" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="J51" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="J52" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="J54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="J55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="J56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="J57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="J59" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="J60" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="J62" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="J63" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="J65" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="J66" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="J67" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
